--- a/Output.xlsx
+++ b/Output.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Annual Waterfall" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Quarterly Waterfall" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Original Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Top Customers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Intermediate Calcs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Quarterly Waterfall" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Original Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Top Customers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -141,6 +142,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -596,15 +598,15 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$C$105</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$D$105</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$E$105</f>
         <v/>
       </c>
     </row>
@@ -616,15 +618,15 @@
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*'Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$C$106</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$D$106</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*'Original Data'!$AM$4:$AM$103)*12</f>
+        <f>'Intermediate Calcs'!$E$106</f>
         <v/>
       </c>
     </row>
@@ -636,15 +638,15 @@
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&gt;'Original Data'!$C$4:$C$103)*('Original Data'!$O$4:$O$103-'Original Data'!$C$4:$C$103))*12</f>
+        <f>'Intermediate Calcs'!$C$107</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;'Original Data'!$O$4:$O$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$O$4:$O$103))*12</f>
+        <f>'Intermediate Calcs'!$D$107</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <f>'Intermediate Calcs'!$E$107</f>
         <v/>
       </c>
     </row>
@@ -656,15 +658,15 @@
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&lt;'Original Data'!$C$4:$C$103)*('Original Data'!$O$4:$O$103-'Original Data'!$C$4:$C$103))*12</f>
+        <f>'Intermediate Calcs'!$C$108</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;'Original Data'!$O$4:$O$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$O$4:$O$103))*12</f>
+        <f>'Intermediate Calcs'!$D$108</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <f>'Intermediate Calcs'!$E$108</f>
         <v/>
       </c>
     </row>
@@ -676,15 +678,15 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*'Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$C$109</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*'Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$D$109</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$E$109</f>
         <v/>
       </c>
     </row>
@@ -695,19 +697,19 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$B$110</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$C$110</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$D$110</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>SUM('Original Data'!$AM$4:$AM$103)*12</f>
+        <f>'Intermediate Calcs'!$E$110</f>
         <v/>
       </c>
     </row>
@@ -870,15 +872,15 @@
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="16">
-        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$C$112</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$D$112</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$E$112</f>
         <v/>
       </c>
     </row>
@@ -890,15 +892,15 @@
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="16">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$C$113</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$D$113</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$E$113</f>
         <v/>
       </c>
     </row>
@@ -910,15 +912,15 @@
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="17">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$C$114</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$D$114</f>
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$E$114</f>
         <v/>
       </c>
     </row>
@@ -929,19 +931,19 @@
         </is>
       </c>
       <c r="B20" s="18">
-        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$B$115</f>
         <v/>
       </c>
       <c r="C20" s="18">
-        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$C$115</f>
         <v/>
       </c>
       <c r="D20" s="18">
-        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$D$115</f>
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>COUNTIF('Original Data'!$AM$4:$AM$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$E$115</f>
         <v/>
       </c>
     </row>
@@ -1119,6 +1121,3545 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Intermediate Calculations</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Dec-22</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Dec-23</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Dec-24</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Dec-25</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Original Data'!$B$4</f>
+        <v/>
+      </c>
+      <c r="B3" s="20">
+        <f>'Original Data'!$C$4*12</f>
+        <v/>
+      </c>
+      <c r="C3" s="20">
+        <f>'Original Data'!$O$4*12</f>
+        <v/>
+      </c>
+      <c r="D3" s="20">
+        <f>'Original Data'!$AA$4*12</f>
+        <v/>
+      </c>
+      <c r="E3" s="20">
+        <f>'Original Data'!$AM$4*12</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IF($E3&gt;10,RANK($E3,$E$3:$E$102,0)+COUNTIF($E$3:$E3,$E3)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Original Data'!$B$5</f>
+        <v/>
+      </c>
+      <c r="B4" s="20">
+        <f>'Original Data'!$C$5*12</f>
+        <v/>
+      </c>
+      <c r="C4" s="20">
+        <f>'Original Data'!$O$5*12</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>'Original Data'!$AA$5*12</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>'Original Data'!$AM$5*12</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IF($E4&gt;10,RANK($E4,$E$3:$E$102,0)+COUNTIF($E$3:$E4,$E4)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Original Data'!$B$6</f>
+        <v/>
+      </c>
+      <c r="B5" s="20">
+        <f>'Original Data'!$C$6*12</f>
+        <v/>
+      </c>
+      <c r="C5" s="20">
+        <f>'Original Data'!$O$6*12</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>'Original Data'!$AA$6*12</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>'Original Data'!$AM$6*12</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IF($E5&gt;10,RANK($E5,$E$3:$E$102,0)+COUNTIF($E$3:$E5,$E5)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Original Data'!$B$7</f>
+        <v/>
+      </c>
+      <c r="B6" s="20">
+        <f>'Original Data'!$C$7*12</f>
+        <v/>
+      </c>
+      <c r="C6" s="20">
+        <f>'Original Data'!$O$7*12</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>'Original Data'!$AA$7*12</f>
+        <v/>
+      </c>
+      <c r="E6" s="20">
+        <f>'Original Data'!$AM$7*12</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IF($E6&gt;10,RANK($E6,$E$3:$E$102,0)+COUNTIF($E$3:$E6,$E6)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Original Data'!$B$8</f>
+        <v/>
+      </c>
+      <c r="B7" s="20">
+        <f>'Original Data'!$C$8*12</f>
+        <v/>
+      </c>
+      <c r="C7" s="20">
+        <f>'Original Data'!$O$8*12</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>'Original Data'!$AA$8*12</f>
+        <v/>
+      </c>
+      <c r="E7" s="20">
+        <f>'Original Data'!$AM$8*12</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IF($E7&gt;10,RANK($E7,$E$3:$E$102,0)+COUNTIF($E$3:$E7,$E7)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Original Data'!$B$9</f>
+        <v/>
+      </c>
+      <c r="B8" s="20">
+        <f>'Original Data'!$C$9*12</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>'Original Data'!$O$9*12</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>'Original Data'!$AA$9*12</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>'Original Data'!$AM$9*12</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IF($E8&gt;10,RANK($E8,$E$3:$E$102,0)+COUNTIF($E$3:$E8,$E8)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Original Data'!$B$10</f>
+        <v/>
+      </c>
+      <c r="B9" s="20">
+        <f>'Original Data'!$C$10*12</f>
+        <v/>
+      </c>
+      <c r="C9" s="20">
+        <f>'Original Data'!$O$10*12</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>'Original Data'!$AA$10*12</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>'Original Data'!$AM$10*12</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>IF($E9&gt;10,RANK($E9,$E$3:$E$102,0)+COUNTIF($E$3:$E9,$E9)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Original Data'!$B$11</f>
+        <v/>
+      </c>
+      <c r="B10" s="20">
+        <f>'Original Data'!$C$11*12</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f>'Original Data'!$O$11*12</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>'Original Data'!$AA$11*12</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>'Original Data'!$AM$11*12</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>IF($E10&gt;10,RANK($E10,$E$3:$E$102,0)+COUNTIF($E$3:$E10,$E10)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Original Data'!$B$12</f>
+        <v/>
+      </c>
+      <c r="B11" s="20">
+        <f>'Original Data'!$C$12*12</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>'Original Data'!$O$12*12</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>'Original Data'!$AA$12*12</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>'Original Data'!$AM$12*12</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>IF($E11&gt;10,RANK($E11,$E$3:$E$102,0)+COUNTIF($E$3:$E11,$E11)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Original Data'!$B$13</f>
+        <v/>
+      </c>
+      <c r="B12" s="20">
+        <f>'Original Data'!$C$13*12</f>
+        <v/>
+      </c>
+      <c r="C12" s="20">
+        <f>'Original Data'!$O$13*12</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>'Original Data'!$AA$13*12</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f>'Original Data'!$AM$13*12</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>IF($E12&gt;10,RANK($E12,$E$3:$E$102,0)+COUNTIF($E$3:$E12,$E12)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>'Original Data'!$B$14</f>
+        <v/>
+      </c>
+      <c r="B13" s="20">
+        <f>'Original Data'!$C$14*12</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>'Original Data'!$O$14*12</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>'Original Data'!$AA$14*12</f>
+        <v/>
+      </c>
+      <c r="E13" s="20">
+        <f>'Original Data'!$AM$14*12</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>IF($E13&gt;10,RANK($E13,$E$3:$E$102,0)+COUNTIF($E$3:$E13,$E13)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>'Original Data'!$B$15</f>
+        <v/>
+      </c>
+      <c r="B14" s="20">
+        <f>'Original Data'!$C$15*12</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>'Original Data'!$O$15*12</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>'Original Data'!$AA$15*12</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f>'Original Data'!$AM$15*12</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f>IF($E14&gt;10,RANK($E14,$E$3:$E$102,0)+COUNTIF($E$3:$E14,$E14)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <f>'Original Data'!$B$16</f>
+        <v/>
+      </c>
+      <c r="B15" s="20">
+        <f>'Original Data'!$C$16*12</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>'Original Data'!$O$16*12</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>'Original Data'!$AA$16*12</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>'Original Data'!$AM$16*12</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>IF($E15&gt;10,RANK($E15,$E$3:$E$102,0)+COUNTIF($E$3:$E15,$E15)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <f>'Original Data'!$B$17</f>
+        <v/>
+      </c>
+      <c r="B16" s="20">
+        <f>'Original Data'!$C$17*12</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>'Original Data'!$O$17*12</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f>'Original Data'!$AA$17*12</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f>'Original Data'!$AM$17*12</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>IF($E16&gt;10,RANK($E16,$E$3:$E$102,0)+COUNTIF($E$3:$E16,$E16)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <f>'Original Data'!$B$18</f>
+        <v/>
+      </c>
+      <c r="B17" s="20">
+        <f>'Original Data'!$C$18*12</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>'Original Data'!$O$18*12</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>'Original Data'!$AA$18*12</f>
+        <v/>
+      </c>
+      <c r="E17" s="20">
+        <f>'Original Data'!$AM$18*12</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>IF($E17&gt;10,RANK($E17,$E$3:$E$102,0)+COUNTIF($E$3:$E17,$E17)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <f>'Original Data'!$B$19</f>
+        <v/>
+      </c>
+      <c r="B18" s="20">
+        <f>'Original Data'!$C$19*12</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>'Original Data'!$O$19*12</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>'Original Data'!$AA$19*12</f>
+        <v/>
+      </c>
+      <c r="E18" s="20">
+        <f>'Original Data'!$AM$19*12</f>
+        <v/>
+      </c>
+      <c r="F18">
+        <f>IF($E18&gt;10,RANK($E18,$E$3:$E$102,0)+COUNTIF($E$3:$E18,$E18)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <f>'Original Data'!$B$20</f>
+        <v/>
+      </c>
+      <c r="B19" s="20">
+        <f>'Original Data'!$C$20*12</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>'Original Data'!$O$20*12</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>'Original Data'!$AA$20*12</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>'Original Data'!$AM$20*12</f>
+        <v/>
+      </c>
+      <c r="F19">
+        <f>IF($E19&gt;10,RANK($E19,$E$3:$E$102,0)+COUNTIF($E$3:$E19,$E19)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <f>'Original Data'!$B$21</f>
+        <v/>
+      </c>
+      <c r="B20" s="20">
+        <f>'Original Data'!$C$21*12</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>'Original Data'!$O$21*12</f>
+        <v/>
+      </c>
+      <c r="D20" s="20">
+        <f>'Original Data'!$AA$21*12</f>
+        <v/>
+      </c>
+      <c r="E20" s="20">
+        <f>'Original Data'!$AM$21*12</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>IF($E20&gt;10,RANK($E20,$E$3:$E$102,0)+COUNTIF($E$3:$E20,$E20)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <f>'Original Data'!$B$22</f>
+        <v/>
+      </c>
+      <c r="B21" s="20">
+        <f>'Original Data'!$C$22*12</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>'Original Data'!$O$22*12</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f>'Original Data'!$AA$22*12</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f>'Original Data'!$AM$22*12</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>IF($E21&gt;10,RANK($E21,$E$3:$E$102,0)+COUNTIF($E$3:$E21,$E21)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>'Original Data'!$B$23</f>
+        <v/>
+      </c>
+      <c r="B22" s="20">
+        <f>'Original Data'!$C$23*12</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>'Original Data'!$O$23*12</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>'Original Data'!$AA$23*12</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>'Original Data'!$AM$23*12</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>IF($E22&gt;10,RANK($E22,$E$3:$E$102,0)+COUNTIF($E$3:$E22,$E22)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <f>'Original Data'!$B$24</f>
+        <v/>
+      </c>
+      <c r="B23" s="20">
+        <f>'Original Data'!$C$24*12</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>'Original Data'!$O$24*12</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>'Original Data'!$AA$24*12</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f>'Original Data'!$AM$24*12</f>
+        <v/>
+      </c>
+      <c r="F23">
+        <f>IF($E23&gt;10,RANK($E23,$E$3:$E$102,0)+COUNTIF($E$3:$E23,$E23)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <f>'Original Data'!$B$25</f>
+        <v/>
+      </c>
+      <c r="B24" s="20">
+        <f>'Original Data'!$C$25*12</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>'Original Data'!$O$25*12</f>
+        <v/>
+      </c>
+      <c r="D24" s="20">
+        <f>'Original Data'!$AA$25*12</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>'Original Data'!$AM$25*12</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>IF($E24&gt;10,RANK($E24,$E$3:$E$102,0)+COUNTIF($E$3:$E24,$E24)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <f>'Original Data'!$B$26</f>
+        <v/>
+      </c>
+      <c r="B25" s="20">
+        <f>'Original Data'!$C$26*12</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>'Original Data'!$O$26*12</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f>'Original Data'!$AA$26*12</f>
+        <v/>
+      </c>
+      <c r="E25" s="20">
+        <f>'Original Data'!$AM$26*12</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>IF($E25&gt;10,RANK($E25,$E$3:$E$102,0)+COUNTIF($E$3:$E25,$E25)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <f>'Original Data'!$B$27</f>
+        <v/>
+      </c>
+      <c r="B26" s="20">
+        <f>'Original Data'!$C$27*12</f>
+        <v/>
+      </c>
+      <c r="C26" s="20">
+        <f>'Original Data'!$O$27*12</f>
+        <v/>
+      </c>
+      <c r="D26" s="20">
+        <f>'Original Data'!$AA$27*12</f>
+        <v/>
+      </c>
+      <c r="E26" s="20">
+        <f>'Original Data'!$AM$27*12</f>
+        <v/>
+      </c>
+      <c r="F26">
+        <f>IF($E26&gt;10,RANK($E26,$E$3:$E$102,0)+COUNTIF($E$3:$E26,$E26)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>'Original Data'!$B$28</f>
+        <v/>
+      </c>
+      <c r="B27" s="20">
+        <f>'Original Data'!$C$28*12</f>
+        <v/>
+      </c>
+      <c r="C27" s="20">
+        <f>'Original Data'!$O$28*12</f>
+        <v/>
+      </c>
+      <c r="D27" s="20">
+        <f>'Original Data'!$AA$28*12</f>
+        <v/>
+      </c>
+      <c r="E27" s="20">
+        <f>'Original Data'!$AM$28*12</f>
+        <v/>
+      </c>
+      <c r="F27">
+        <f>IF($E27&gt;10,RANK($E27,$E$3:$E$102,0)+COUNTIF($E$3:$E27,$E27)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <f>'Original Data'!$B$29</f>
+        <v/>
+      </c>
+      <c r="B28" s="20">
+        <f>'Original Data'!$C$29*12</f>
+        <v/>
+      </c>
+      <c r="C28" s="20">
+        <f>'Original Data'!$O$29*12</f>
+        <v/>
+      </c>
+      <c r="D28" s="20">
+        <f>'Original Data'!$AA$29*12</f>
+        <v/>
+      </c>
+      <c r="E28" s="20">
+        <f>'Original Data'!$AM$29*12</f>
+        <v/>
+      </c>
+      <c r="F28">
+        <f>IF($E28&gt;10,RANK($E28,$E$3:$E$102,0)+COUNTIF($E$3:$E28,$E28)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>'Original Data'!$B$30</f>
+        <v/>
+      </c>
+      <c r="B29" s="20">
+        <f>'Original Data'!$C$30*12</f>
+        <v/>
+      </c>
+      <c r="C29" s="20">
+        <f>'Original Data'!$O$30*12</f>
+        <v/>
+      </c>
+      <c r="D29" s="20">
+        <f>'Original Data'!$AA$30*12</f>
+        <v/>
+      </c>
+      <c r="E29" s="20">
+        <f>'Original Data'!$AM$30*12</f>
+        <v/>
+      </c>
+      <c r="F29">
+        <f>IF($E29&gt;10,RANK($E29,$E$3:$E$102,0)+COUNTIF($E$3:$E29,$E29)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <f>'Original Data'!$B$31</f>
+        <v/>
+      </c>
+      <c r="B30" s="20">
+        <f>'Original Data'!$C$31*12</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f>'Original Data'!$O$31*12</f>
+        <v/>
+      </c>
+      <c r="D30" s="20">
+        <f>'Original Data'!$AA$31*12</f>
+        <v/>
+      </c>
+      <c r="E30" s="20">
+        <f>'Original Data'!$AM$31*12</f>
+        <v/>
+      </c>
+      <c r="F30">
+        <f>IF($E30&gt;10,RANK($E30,$E$3:$E$102,0)+COUNTIF($E$3:$E30,$E30)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <f>'Original Data'!$B$32</f>
+        <v/>
+      </c>
+      <c r="B31" s="20">
+        <f>'Original Data'!$C$32*12</f>
+        <v/>
+      </c>
+      <c r="C31" s="20">
+        <f>'Original Data'!$O$32*12</f>
+        <v/>
+      </c>
+      <c r="D31" s="20">
+        <f>'Original Data'!$AA$32*12</f>
+        <v/>
+      </c>
+      <c r="E31" s="20">
+        <f>'Original Data'!$AM$32*12</f>
+        <v/>
+      </c>
+      <c r="F31">
+        <f>IF($E31&gt;10,RANK($E31,$E$3:$E$102,0)+COUNTIF($E$3:$E31,$E31)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <f>'Original Data'!$B$33</f>
+        <v/>
+      </c>
+      <c r="B32" s="20">
+        <f>'Original Data'!$C$33*12</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f>'Original Data'!$O$33*12</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f>'Original Data'!$AA$33*12</f>
+        <v/>
+      </c>
+      <c r="E32" s="20">
+        <f>'Original Data'!$AM$33*12</f>
+        <v/>
+      </c>
+      <c r="F32">
+        <f>IF($E32&gt;10,RANK($E32,$E$3:$E$102,0)+COUNTIF($E$3:$E32,$E32)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <f>'Original Data'!$B$34</f>
+        <v/>
+      </c>
+      <c r="B33" s="20">
+        <f>'Original Data'!$C$34*12</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>'Original Data'!$O$34*12</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
+        <f>'Original Data'!$AA$34*12</f>
+        <v/>
+      </c>
+      <c r="E33" s="20">
+        <f>'Original Data'!$AM$34*12</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>IF($E33&gt;10,RANK($E33,$E$3:$E$102,0)+COUNTIF($E$3:$E33,$E33)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <f>'Original Data'!$B$35</f>
+        <v/>
+      </c>
+      <c r="B34" s="20">
+        <f>'Original Data'!$C$35*12</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f>'Original Data'!$O$35*12</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f>'Original Data'!$AA$35*12</f>
+        <v/>
+      </c>
+      <c r="E34" s="20">
+        <f>'Original Data'!$AM$35*12</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>IF($E34&gt;10,RANK($E34,$E$3:$E$102,0)+COUNTIF($E$3:$E34,$E34)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>'Original Data'!$B$36</f>
+        <v/>
+      </c>
+      <c r="B35" s="20">
+        <f>'Original Data'!$C$36*12</f>
+        <v/>
+      </c>
+      <c r="C35" s="20">
+        <f>'Original Data'!$O$36*12</f>
+        <v/>
+      </c>
+      <c r="D35" s="20">
+        <f>'Original Data'!$AA$36*12</f>
+        <v/>
+      </c>
+      <c r="E35" s="20">
+        <f>'Original Data'!$AM$36*12</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>IF($E35&gt;10,RANK($E35,$E$3:$E$102,0)+COUNTIF($E$3:$E35,$E35)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <f>'Original Data'!$B$37</f>
+        <v/>
+      </c>
+      <c r="B36" s="20">
+        <f>'Original Data'!$C$37*12</f>
+        <v/>
+      </c>
+      <c r="C36" s="20">
+        <f>'Original Data'!$O$37*12</f>
+        <v/>
+      </c>
+      <c r="D36" s="20">
+        <f>'Original Data'!$AA$37*12</f>
+        <v/>
+      </c>
+      <c r="E36" s="20">
+        <f>'Original Data'!$AM$37*12</f>
+        <v/>
+      </c>
+      <c r="F36">
+        <f>IF($E36&gt;10,RANK($E36,$E$3:$E$102,0)+COUNTIF($E$3:$E36,$E36)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <f>'Original Data'!$B$38</f>
+        <v/>
+      </c>
+      <c r="B37" s="20">
+        <f>'Original Data'!$C$38*12</f>
+        <v/>
+      </c>
+      <c r="C37" s="20">
+        <f>'Original Data'!$O$38*12</f>
+        <v/>
+      </c>
+      <c r="D37" s="20">
+        <f>'Original Data'!$AA$38*12</f>
+        <v/>
+      </c>
+      <c r="E37" s="20">
+        <f>'Original Data'!$AM$38*12</f>
+        <v/>
+      </c>
+      <c r="F37">
+        <f>IF($E37&gt;10,RANK($E37,$E$3:$E$102,0)+COUNTIF($E$3:$E37,$E37)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>'Original Data'!$B$39</f>
+        <v/>
+      </c>
+      <c r="B38" s="20">
+        <f>'Original Data'!$C$39*12</f>
+        <v/>
+      </c>
+      <c r="C38" s="20">
+        <f>'Original Data'!$O$39*12</f>
+        <v/>
+      </c>
+      <c r="D38" s="20">
+        <f>'Original Data'!$AA$39*12</f>
+        <v/>
+      </c>
+      <c r="E38" s="20">
+        <f>'Original Data'!$AM$39*12</f>
+        <v/>
+      </c>
+      <c r="F38">
+        <f>IF($E38&gt;10,RANK($E38,$E$3:$E$102,0)+COUNTIF($E$3:$E38,$E38)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>'Original Data'!$B$40</f>
+        <v/>
+      </c>
+      <c r="B39" s="20">
+        <f>'Original Data'!$C$40*12</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>'Original Data'!$O$40*12</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>'Original Data'!$AA$40*12</f>
+        <v/>
+      </c>
+      <c r="E39" s="20">
+        <f>'Original Data'!$AM$40*12</f>
+        <v/>
+      </c>
+      <c r="F39">
+        <f>IF($E39&gt;10,RANK($E39,$E$3:$E$102,0)+COUNTIF($E$3:$E39,$E39)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <f>'Original Data'!$B$41</f>
+        <v/>
+      </c>
+      <c r="B40" s="20">
+        <f>'Original Data'!$C$41*12</f>
+        <v/>
+      </c>
+      <c r="C40" s="20">
+        <f>'Original Data'!$O$41*12</f>
+        <v/>
+      </c>
+      <c r="D40" s="20">
+        <f>'Original Data'!$AA$41*12</f>
+        <v/>
+      </c>
+      <c r="E40" s="20">
+        <f>'Original Data'!$AM$41*12</f>
+        <v/>
+      </c>
+      <c r="F40">
+        <f>IF($E40&gt;10,RANK($E40,$E$3:$E$102,0)+COUNTIF($E$3:$E40,$E40)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>'Original Data'!$B$42</f>
+        <v/>
+      </c>
+      <c r="B41" s="20">
+        <f>'Original Data'!$C$42*12</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f>'Original Data'!$O$42*12</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
+        <f>'Original Data'!$AA$42*12</f>
+        <v/>
+      </c>
+      <c r="E41" s="20">
+        <f>'Original Data'!$AM$42*12</f>
+        <v/>
+      </c>
+      <c r="F41">
+        <f>IF($E41&gt;10,RANK($E41,$E$3:$E$102,0)+COUNTIF($E$3:$E41,$E41)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <f>'Original Data'!$B$43</f>
+        <v/>
+      </c>
+      <c r="B42" s="20">
+        <f>'Original Data'!$C$43*12</f>
+        <v/>
+      </c>
+      <c r="C42" s="20">
+        <f>'Original Data'!$O$43*12</f>
+        <v/>
+      </c>
+      <c r="D42" s="20">
+        <f>'Original Data'!$AA$43*12</f>
+        <v/>
+      </c>
+      <c r="E42" s="20">
+        <f>'Original Data'!$AM$43*12</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>IF($E42&gt;10,RANK($E42,$E$3:$E$102,0)+COUNTIF($E$3:$E42,$E42)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <f>'Original Data'!$B$44</f>
+        <v/>
+      </c>
+      <c r="B43" s="20">
+        <f>'Original Data'!$C$44*12</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>'Original Data'!$O$44*12</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f>'Original Data'!$AA$44*12</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>'Original Data'!$AM$44*12</f>
+        <v/>
+      </c>
+      <c r="F43">
+        <f>IF($E43&gt;10,RANK($E43,$E$3:$E$102,0)+COUNTIF($E$3:$E43,$E43)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>'Original Data'!$B$45</f>
+        <v/>
+      </c>
+      <c r="B44" s="20">
+        <f>'Original Data'!$C$45*12</f>
+        <v/>
+      </c>
+      <c r="C44" s="20">
+        <f>'Original Data'!$O$45*12</f>
+        <v/>
+      </c>
+      <c r="D44" s="20">
+        <f>'Original Data'!$AA$45*12</f>
+        <v/>
+      </c>
+      <c r="E44" s="20">
+        <f>'Original Data'!$AM$45*12</f>
+        <v/>
+      </c>
+      <c r="F44">
+        <f>IF($E44&gt;10,RANK($E44,$E$3:$E$102,0)+COUNTIF($E$3:$E44,$E44)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <f>'Original Data'!$B$46</f>
+        <v/>
+      </c>
+      <c r="B45" s="20">
+        <f>'Original Data'!$C$46*12</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f>'Original Data'!$O$46*12</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
+        <f>'Original Data'!$AA$46*12</f>
+        <v/>
+      </c>
+      <c r="E45" s="20">
+        <f>'Original Data'!$AM$46*12</f>
+        <v/>
+      </c>
+      <c r="F45">
+        <f>IF($E45&gt;10,RANK($E45,$E$3:$E$102,0)+COUNTIF($E$3:$E45,$E45)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <f>'Original Data'!$B$47</f>
+        <v/>
+      </c>
+      <c r="B46" s="20">
+        <f>'Original Data'!$C$47*12</f>
+        <v/>
+      </c>
+      <c r="C46" s="20">
+        <f>'Original Data'!$O$47*12</f>
+        <v/>
+      </c>
+      <c r="D46" s="20">
+        <f>'Original Data'!$AA$47*12</f>
+        <v/>
+      </c>
+      <c r="E46" s="20">
+        <f>'Original Data'!$AM$47*12</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>IF($E46&gt;10,RANK($E46,$E$3:$E$102,0)+COUNTIF($E$3:$E46,$E46)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <f>'Original Data'!$B$48</f>
+        <v/>
+      </c>
+      <c r="B47" s="20">
+        <f>'Original Data'!$C$48*12</f>
+        <v/>
+      </c>
+      <c r="C47" s="20">
+        <f>'Original Data'!$O$48*12</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
+        <f>'Original Data'!$AA$48*12</f>
+        <v/>
+      </c>
+      <c r="E47" s="20">
+        <f>'Original Data'!$AM$48*12</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>IF($E47&gt;10,RANK($E47,$E$3:$E$102,0)+COUNTIF($E$3:$E47,$E47)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <f>'Original Data'!$B$49</f>
+        <v/>
+      </c>
+      <c r="B48" s="20">
+        <f>'Original Data'!$C$49*12</f>
+        <v/>
+      </c>
+      <c r="C48" s="20">
+        <f>'Original Data'!$O$49*12</f>
+        <v/>
+      </c>
+      <c r="D48" s="20">
+        <f>'Original Data'!$AA$49*12</f>
+        <v/>
+      </c>
+      <c r="E48" s="20">
+        <f>'Original Data'!$AM$49*12</f>
+        <v/>
+      </c>
+      <c r="F48">
+        <f>IF($E48&gt;10,RANK($E48,$E$3:$E$102,0)+COUNTIF($E$3:$E48,$E48)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <f>'Original Data'!$B$50</f>
+        <v/>
+      </c>
+      <c r="B49" s="20">
+        <f>'Original Data'!$C$50*12</f>
+        <v/>
+      </c>
+      <c r="C49" s="20">
+        <f>'Original Data'!$O$50*12</f>
+        <v/>
+      </c>
+      <c r="D49" s="20">
+        <f>'Original Data'!$AA$50*12</f>
+        <v/>
+      </c>
+      <c r="E49" s="20">
+        <f>'Original Data'!$AM$50*12</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>IF($E49&gt;10,RANK($E49,$E$3:$E$102,0)+COUNTIF($E$3:$E49,$E49)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <f>'Original Data'!$B$51</f>
+        <v/>
+      </c>
+      <c r="B50" s="20">
+        <f>'Original Data'!$C$51*12</f>
+        <v/>
+      </c>
+      <c r="C50" s="20">
+        <f>'Original Data'!$O$51*12</f>
+        <v/>
+      </c>
+      <c r="D50" s="20">
+        <f>'Original Data'!$AA$51*12</f>
+        <v/>
+      </c>
+      <c r="E50" s="20">
+        <f>'Original Data'!$AM$51*12</f>
+        <v/>
+      </c>
+      <c r="F50">
+        <f>IF($E50&gt;10,RANK($E50,$E$3:$E$102,0)+COUNTIF($E$3:$E50,$E50)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <f>'Original Data'!$B$52</f>
+        <v/>
+      </c>
+      <c r="B51" s="20">
+        <f>'Original Data'!$C$52*12</f>
+        <v/>
+      </c>
+      <c r="C51" s="20">
+        <f>'Original Data'!$O$52*12</f>
+        <v/>
+      </c>
+      <c r="D51" s="20">
+        <f>'Original Data'!$AA$52*12</f>
+        <v/>
+      </c>
+      <c r="E51" s="20">
+        <f>'Original Data'!$AM$52*12</f>
+        <v/>
+      </c>
+      <c r="F51">
+        <f>IF($E51&gt;10,RANK($E51,$E$3:$E$102,0)+COUNTIF($E$3:$E51,$E51)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <f>'Original Data'!$B$53</f>
+        <v/>
+      </c>
+      <c r="B52" s="20">
+        <f>'Original Data'!$C$53*12</f>
+        <v/>
+      </c>
+      <c r="C52" s="20">
+        <f>'Original Data'!$O$53*12</f>
+        <v/>
+      </c>
+      <c r="D52" s="20">
+        <f>'Original Data'!$AA$53*12</f>
+        <v/>
+      </c>
+      <c r="E52" s="20">
+        <f>'Original Data'!$AM$53*12</f>
+        <v/>
+      </c>
+      <c r="F52">
+        <f>IF($E52&gt;10,RANK($E52,$E$3:$E$102,0)+COUNTIF($E$3:$E52,$E52)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <f>'Original Data'!$B$54</f>
+        <v/>
+      </c>
+      <c r="B53" s="20">
+        <f>'Original Data'!$C$54*12</f>
+        <v/>
+      </c>
+      <c r="C53" s="20">
+        <f>'Original Data'!$O$54*12</f>
+        <v/>
+      </c>
+      <c r="D53" s="20">
+        <f>'Original Data'!$AA$54*12</f>
+        <v/>
+      </c>
+      <c r="E53" s="20">
+        <f>'Original Data'!$AM$54*12</f>
+        <v/>
+      </c>
+      <c r="F53">
+        <f>IF($E53&gt;10,RANK($E53,$E$3:$E$102,0)+COUNTIF($E$3:$E53,$E53)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <f>'Original Data'!$B$55</f>
+        <v/>
+      </c>
+      <c r="B54" s="20">
+        <f>'Original Data'!$C$55*12</f>
+        <v/>
+      </c>
+      <c r="C54" s="20">
+        <f>'Original Data'!$O$55*12</f>
+        <v/>
+      </c>
+      <c r="D54" s="20">
+        <f>'Original Data'!$AA$55*12</f>
+        <v/>
+      </c>
+      <c r="E54" s="20">
+        <f>'Original Data'!$AM$55*12</f>
+        <v/>
+      </c>
+      <c r="F54">
+        <f>IF($E54&gt;10,RANK($E54,$E$3:$E$102,0)+COUNTIF($E$3:$E54,$E54)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>'Original Data'!$B$56</f>
+        <v/>
+      </c>
+      <c r="B55" s="20">
+        <f>'Original Data'!$C$56*12</f>
+        <v/>
+      </c>
+      <c r="C55" s="20">
+        <f>'Original Data'!$O$56*12</f>
+        <v/>
+      </c>
+      <c r="D55" s="20">
+        <f>'Original Data'!$AA$56*12</f>
+        <v/>
+      </c>
+      <c r="E55" s="20">
+        <f>'Original Data'!$AM$56*12</f>
+        <v/>
+      </c>
+      <c r="F55">
+        <f>IF($E55&gt;10,RANK($E55,$E$3:$E$102,0)+COUNTIF($E$3:$E55,$E55)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <f>'Original Data'!$B$57</f>
+        <v/>
+      </c>
+      <c r="B56" s="20">
+        <f>'Original Data'!$C$57*12</f>
+        <v/>
+      </c>
+      <c r="C56" s="20">
+        <f>'Original Data'!$O$57*12</f>
+        <v/>
+      </c>
+      <c r="D56" s="20">
+        <f>'Original Data'!$AA$57*12</f>
+        <v/>
+      </c>
+      <c r="E56" s="20">
+        <f>'Original Data'!$AM$57*12</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>IF($E56&gt;10,RANK($E56,$E$3:$E$102,0)+COUNTIF($E$3:$E56,$E56)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <f>'Original Data'!$B$58</f>
+        <v/>
+      </c>
+      <c r="B57" s="20">
+        <f>'Original Data'!$C$58*12</f>
+        <v/>
+      </c>
+      <c r="C57" s="20">
+        <f>'Original Data'!$O$58*12</f>
+        <v/>
+      </c>
+      <c r="D57" s="20">
+        <f>'Original Data'!$AA$58*12</f>
+        <v/>
+      </c>
+      <c r="E57" s="20">
+        <f>'Original Data'!$AM$58*12</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF($E57&gt;10,RANK($E57,$E$3:$E$102,0)+COUNTIF($E$3:$E57,$E57)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <f>'Original Data'!$B$59</f>
+        <v/>
+      </c>
+      <c r="B58" s="20">
+        <f>'Original Data'!$C$59*12</f>
+        <v/>
+      </c>
+      <c r="C58" s="20">
+        <f>'Original Data'!$O$59*12</f>
+        <v/>
+      </c>
+      <c r="D58" s="20">
+        <f>'Original Data'!$AA$59*12</f>
+        <v/>
+      </c>
+      <c r="E58" s="20">
+        <f>'Original Data'!$AM$59*12</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF($E58&gt;10,RANK($E58,$E$3:$E$102,0)+COUNTIF($E$3:$E58,$E58)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <f>'Original Data'!$B$60</f>
+        <v/>
+      </c>
+      <c r="B59" s="20">
+        <f>'Original Data'!$C$60*12</f>
+        <v/>
+      </c>
+      <c r="C59" s="20">
+        <f>'Original Data'!$O$60*12</f>
+        <v/>
+      </c>
+      <c r="D59" s="20">
+        <f>'Original Data'!$AA$60*12</f>
+        <v/>
+      </c>
+      <c r="E59" s="20">
+        <f>'Original Data'!$AM$60*12</f>
+        <v/>
+      </c>
+      <c r="F59">
+        <f>IF($E59&gt;10,RANK($E59,$E$3:$E$102,0)+COUNTIF($E$3:$E59,$E59)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <f>'Original Data'!$B$61</f>
+        <v/>
+      </c>
+      <c r="B60" s="20">
+        <f>'Original Data'!$C$61*12</f>
+        <v/>
+      </c>
+      <c r="C60" s="20">
+        <f>'Original Data'!$O$61*12</f>
+        <v/>
+      </c>
+      <c r="D60" s="20">
+        <f>'Original Data'!$AA$61*12</f>
+        <v/>
+      </c>
+      <c r="E60" s="20">
+        <f>'Original Data'!$AM$61*12</f>
+        <v/>
+      </c>
+      <c r="F60">
+        <f>IF($E60&gt;10,RANK($E60,$E$3:$E$102,0)+COUNTIF($E$3:$E60,$E60)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <f>'Original Data'!$B$62</f>
+        <v/>
+      </c>
+      <c r="B61" s="20">
+        <f>'Original Data'!$C$62*12</f>
+        <v/>
+      </c>
+      <c r="C61" s="20">
+        <f>'Original Data'!$O$62*12</f>
+        <v/>
+      </c>
+      <c r="D61" s="20">
+        <f>'Original Data'!$AA$62*12</f>
+        <v/>
+      </c>
+      <c r="E61" s="20">
+        <f>'Original Data'!$AM$62*12</f>
+        <v/>
+      </c>
+      <c r="F61">
+        <f>IF($E61&gt;10,RANK($E61,$E$3:$E$102,0)+COUNTIF($E$3:$E61,$E61)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <f>'Original Data'!$B$63</f>
+        <v/>
+      </c>
+      <c r="B62" s="20">
+        <f>'Original Data'!$C$63*12</f>
+        <v/>
+      </c>
+      <c r="C62" s="20">
+        <f>'Original Data'!$O$63*12</f>
+        <v/>
+      </c>
+      <c r="D62" s="20">
+        <f>'Original Data'!$AA$63*12</f>
+        <v/>
+      </c>
+      <c r="E62" s="20">
+        <f>'Original Data'!$AM$63*12</f>
+        <v/>
+      </c>
+      <c r="F62">
+        <f>IF($E62&gt;10,RANK($E62,$E$3:$E$102,0)+COUNTIF($E$3:$E62,$E62)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <f>'Original Data'!$B$64</f>
+        <v/>
+      </c>
+      <c r="B63" s="20">
+        <f>'Original Data'!$C$64*12</f>
+        <v/>
+      </c>
+      <c r="C63" s="20">
+        <f>'Original Data'!$O$64*12</f>
+        <v/>
+      </c>
+      <c r="D63" s="20">
+        <f>'Original Data'!$AA$64*12</f>
+        <v/>
+      </c>
+      <c r="E63" s="20">
+        <f>'Original Data'!$AM$64*12</f>
+        <v/>
+      </c>
+      <c r="F63">
+        <f>IF($E63&gt;10,RANK($E63,$E$3:$E$102,0)+COUNTIF($E$3:$E63,$E63)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <f>'Original Data'!$B$65</f>
+        <v/>
+      </c>
+      <c r="B64" s="20">
+        <f>'Original Data'!$C$65*12</f>
+        <v/>
+      </c>
+      <c r="C64" s="20">
+        <f>'Original Data'!$O$65*12</f>
+        <v/>
+      </c>
+      <c r="D64" s="20">
+        <f>'Original Data'!$AA$65*12</f>
+        <v/>
+      </c>
+      <c r="E64" s="20">
+        <f>'Original Data'!$AM$65*12</f>
+        <v/>
+      </c>
+      <c r="F64">
+        <f>IF($E64&gt;10,RANK($E64,$E$3:$E$102,0)+COUNTIF($E$3:$E64,$E64)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <f>'Original Data'!$B$66</f>
+        <v/>
+      </c>
+      <c r="B65" s="20">
+        <f>'Original Data'!$C$66*12</f>
+        <v/>
+      </c>
+      <c r="C65" s="20">
+        <f>'Original Data'!$O$66*12</f>
+        <v/>
+      </c>
+      <c r="D65" s="20">
+        <f>'Original Data'!$AA$66*12</f>
+        <v/>
+      </c>
+      <c r="E65" s="20">
+        <f>'Original Data'!$AM$66*12</f>
+        <v/>
+      </c>
+      <c r="F65">
+        <f>IF($E65&gt;10,RANK($E65,$E$3:$E$102,0)+COUNTIF($E$3:$E65,$E65)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <f>'Original Data'!$B$67</f>
+        <v/>
+      </c>
+      <c r="B66" s="20">
+        <f>'Original Data'!$C$67*12</f>
+        <v/>
+      </c>
+      <c r="C66" s="20">
+        <f>'Original Data'!$O$67*12</f>
+        <v/>
+      </c>
+      <c r="D66" s="20">
+        <f>'Original Data'!$AA$67*12</f>
+        <v/>
+      </c>
+      <c r="E66" s="20">
+        <f>'Original Data'!$AM$67*12</f>
+        <v/>
+      </c>
+      <c r="F66">
+        <f>IF($E66&gt;10,RANK($E66,$E$3:$E$102,0)+COUNTIF($E$3:$E66,$E66)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <f>'Original Data'!$B$68</f>
+        <v/>
+      </c>
+      <c r="B67" s="20">
+        <f>'Original Data'!$C$68*12</f>
+        <v/>
+      </c>
+      <c r="C67" s="20">
+        <f>'Original Data'!$O$68*12</f>
+        <v/>
+      </c>
+      <c r="D67" s="20">
+        <f>'Original Data'!$AA$68*12</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>'Original Data'!$AM$68*12</f>
+        <v/>
+      </c>
+      <c r="F67">
+        <f>IF($E67&gt;10,RANK($E67,$E$3:$E$102,0)+COUNTIF($E$3:$E67,$E67)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <f>'Original Data'!$B$69</f>
+        <v/>
+      </c>
+      <c r="B68" s="20">
+        <f>'Original Data'!$C$69*12</f>
+        <v/>
+      </c>
+      <c r="C68" s="20">
+        <f>'Original Data'!$O$69*12</f>
+        <v/>
+      </c>
+      <c r="D68" s="20">
+        <f>'Original Data'!$AA$69*12</f>
+        <v/>
+      </c>
+      <c r="E68" s="20">
+        <f>'Original Data'!$AM$69*12</f>
+        <v/>
+      </c>
+      <c r="F68">
+        <f>IF($E68&gt;10,RANK($E68,$E$3:$E$102,0)+COUNTIF($E$3:$E68,$E68)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <f>'Original Data'!$B$70</f>
+        <v/>
+      </c>
+      <c r="B69" s="20">
+        <f>'Original Data'!$C$70*12</f>
+        <v/>
+      </c>
+      <c r="C69" s="20">
+        <f>'Original Data'!$O$70*12</f>
+        <v/>
+      </c>
+      <c r="D69" s="20">
+        <f>'Original Data'!$AA$70*12</f>
+        <v/>
+      </c>
+      <c r="E69" s="20">
+        <f>'Original Data'!$AM$70*12</f>
+        <v/>
+      </c>
+      <c r="F69">
+        <f>IF($E69&gt;10,RANK($E69,$E$3:$E$102,0)+COUNTIF($E$3:$E69,$E69)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <f>'Original Data'!$B$71</f>
+        <v/>
+      </c>
+      <c r="B70" s="20">
+        <f>'Original Data'!$C$71*12</f>
+        <v/>
+      </c>
+      <c r="C70" s="20">
+        <f>'Original Data'!$O$71*12</f>
+        <v/>
+      </c>
+      <c r="D70" s="20">
+        <f>'Original Data'!$AA$71*12</f>
+        <v/>
+      </c>
+      <c r="E70" s="20">
+        <f>'Original Data'!$AM$71*12</f>
+        <v/>
+      </c>
+      <c r="F70">
+        <f>IF($E70&gt;10,RANK($E70,$E$3:$E$102,0)+COUNTIF($E$3:$E70,$E70)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <f>'Original Data'!$B$72</f>
+        <v/>
+      </c>
+      <c r="B71" s="20">
+        <f>'Original Data'!$C$72*12</f>
+        <v/>
+      </c>
+      <c r="C71" s="20">
+        <f>'Original Data'!$O$72*12</f>
+        <v/>
+      </c>
+      <c r="D71" s="20">
+        <f>'Original Data'!$AA$72*12</f>
+        <v/>
+      </c>
+      <c r="E71" s="20">
+        <f>'Original Data'!$AM$72*12</f>
+        <v/>
+      </c>
+      <c r="F71">
+        <f>IF($E71&gt;10,RANK($E71,$E$3:$E$102,0)+COUNTIF($E$3:$E71,$E71)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <f>'Original Data'!$B$73</f>
+        <v/>
+      </c>
+      <c r="B72" s="20">
+        <f>'Original Data'!$C$73*12</f>
+        <v/>
+      </c>
+      <c r="C72" s="20">
+        <f>'Original Data'!$O$73*12</f>
+        <v/>
+      </c>
+      <c r="D72" s="20">
+        <f>'Original Data'!$AA$73*12</f>
+        <v/>
+      </c>
+      <c r="E72" s="20">
+        <f>'Original Data'!$AM$73*12</f>
+        <v/>
+      </c>
+      <c r="F72">
+        <f>IF($E72&gt;10,RANK($E72,$E$3:$E$102,0)+COUNTIF($E$3:$E72,$E72)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <f>'Original Data'!$B$74</f>
+        <v/>
+      </c>
+      <c r="B73" s="20">
+        <f>'Original Data'!$C$74*12</f>
+        <v/>
+      </c>
+      <c r="C73" s="20">
+        <f>'Original Data'!$O$74*12</f>
+        <v/>
+      </c>
+      <c r="D73" s="20">
+        <f>'Original Data'!$AA$74*12</f>
+        <v/>
+      </c>
+      <c r="E73" s="20">
+        <f>'Original Data'!$AM$74*12</f>
+        <v/>
+      </c>
+      <c r="F73">
+        <f>IF($E73&gt;10,RANK($E73,$E$3:$E$102,0)+COUNTIF($E$3:$E73,$E73)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <f>'Original Data'!$B$75</f>
+        <v/>
+      </c>
+      <c r="B74" s="20">
+        <f>'Original Data'!$C$75*12</f>
+        <v/>
+      </c>
+      <c r="C74" s="20">
+        <f>'Original Data'!$O$75*12</f>
+        <v/>
+      </c>
+      <c r="D74" s="20">
+        <f>'Original Data'!$AA$75*12</f>
+        <v/>
+      </c>
+      <c r="E74" s="20">
+        <f>'Original Data'!$AM$75*12</f>
+        <v/>
+      </c>
+      <c r="F74">
+        <f>IF($E74&gt;10,RANK($E74,$E$3:$E$102,0)+COUNTIF($E$3:$E74,$E74)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <f>'Original Data'!$B$76</f>
+        <v/>
+      </c>
+      <c r="B75" s="20">
+        <f>'Original Data'!$C$76*12</f>
+        <v/>
+      </c>
+      <c r="C75" s="20">
+        <f>'Original Data'!$O$76*12</f>
+        <v/>
+      </c>
+      <c r="D75" s="20">
+        <f>'Original Data'!$AA$76*12</f>
+        <v/>
+      </c>
+      <c r="E75" s="20">
+        <f>'Original Data'!$AM$76*12</f>
+        <v/>
+      </c>
+      <c r="F75">
+        <f>IF($E75&gt;10,RANK($E75,$E$3:$E$102,0)+COUNTIF($E$3:$E75,$E75)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <f>'Original Data'!$B$77</f>
+        <v/>
+      </c>
+      <c r="B76" s="20">
+        <f>'Original Data'!$C$77*12</f>
+        <v/>
+      </c>
+      <c r="C76" s="20">
+        <f>'Original Data'!$O$77*12</f>
+        <v/>
+      </c>
+      <c r="D76" s="20">
+        <f>'Original Data'!$AA$77*12</f>
+        <v/>
+      </c>
+      <c r="E76" s="20">
+        <f>'Original Data'!$AM$77*12</f>
+        <v/>
+      </c>
+      <c r="F76">
+        <f>IF($E76&gt;10,RANK($E76,$E$3:$E$102,0)+COUNTIF($E$3:$E76,$E76)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <f>'Original Data'!$B$78</f>
+        <v/>
+      </c>
+      <c r="B77" s="20">
+        <f>'Original Data'!$C$78*12</f>
+        <v/>
+      </c>
+      <c r="C77" s="20">
+        <f>'Original Data'!$O$78*12</f>
+        <v/>
+      </c>
+      <c r="D77" s="20">
+        <f>'Original Data'!$AA$78*12</f>
+        <v/>
+      </c>
+      <c r="E77" s="20">
+        <f>'Original Data'!$AM$78*12</f>
+        <v/>
+      </c>
+      <c r="F77">
+        <f>IF($E77&gt;10,RANK($E77,$E$3:$E$102,0)+COUNTIF($E$3:$E77,$E77)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <f>'Original Data'!$B$79</f>
+        <v/>
+      </c>
+      <c r="B78" s="20">
+        <f>'Original Data'!$C$79*12</f>
+        <v/>
+      </c>
+      <c r="C78" s="20">
+        <f>'Original Data'!$O$79*12</f>
+        <v/>
+      </c>
+      <c r="D78" s="20">
+        <f>'Original Data'!$AA$79*12</f>
+        <v/>
+      </c>
+      <c r="E78" s="20">
+        <f>'Original Data'!$AM$79*12</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>IF($E78&gt;10,RANK($E78,$E$3:$E$102,0)+COUNTIF($E$3:$E78,$E78)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <f>'Original Data'!$B$80</f>
+        <v/>
+      </c>
+      <c r="B79" s="20">
+        <f>'Original Data'!$C$80*12</f>
+        <v/>
+      </c>
+      <c r="C79" s="20">
+        <f>'Original Data'!$O$80*12</f>
+        <v/>
+      </c>
+      <c r="D79" s="20">
+        <f>'Original Data'!$AA$80*12</f>
+        <v/>
+      </c>
+      <c r="E79" s="20">
+        <f>'Original Data'!$AM$80*12</f>
+        <v/>
+      </c>
+      <c r="F79">
+        <f>IF($E79&gt;10,RANK($E79,$E$3:$E$102,0)+COUNTIF($E$3:$E79,$E79)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>'Original Data'!$B$81</f>
+        <v/>
+      </c>
+      <c r="B80" s="20">
+        <f>'Original Data'!$C$81*12</f>
+        <v/>
+      </c>
+      <c r="C80" s="20">
+        <f>'Original Data'!$O$81*12</f>
+        <v/>
+      </c>
+      <c r="D80" s="20">
+        <f>'Original Data'!$AA$81*12</f>
+        <v/>
+      </c>
+      <c r="E80" s="20">
+        <f>'Original Data'!$AM$81*12</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>IF($E80&gt;10,RANK($E80,$E$3:$E$102,0)+COUNTIF($E$3:$E80,$E80)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <f>'Original Data'!$B$82</f>
+        <v/>
+      </c>
+      <c r="B81" s="20">
+        <f>'Original Data'!$C$82*12</f>
+        <v/>
+      </c>
+      <c r="C81" s="20">
+        <f>'Original Data'!$O$82*12</f>
+        <v/>
+      </c>
+      <c r="D81" s="20">
+        <f>'Original Data'!$AA$82*12</f>
+        <v/>
+      </c>
+      <c r="E81" s="20">
+        <f>'Original Data'!$AM$82*12</f>
+        <v/>
+      </c>
+      <c r="F81">
+        <f>IF($E81&gt;10,RANK($E81,$E$3:$E$102,0)+COUNTIF($E$3:$E81,$E81)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <f>'Original Data'!$B$83</f>
+        <v/>
+      </c>
+      <c r="B82" s="20">
+        <f>'Original Data'!$C$83*12</f>
+        <v/>
+      </c>
+      <c r="C82" s="20">
+        <f>'Original Data'!$O$83*12</f>
+        <v/>
+      </c>
+      <c r="D82" s="20">
+        <f>'Original Data'!$AA$83*12</f>
+        <v/>
+      </c>
+      <c r="E82" s="20">
+        <f>'Original Data'!$AM$83*12</f>
+        <v/>
+      </c>
+      <c r="F82">
+        <f>IF($E82&gt;10,RANK($E82,$E$3:$E$102,0)+COUNTIF($E$3:$E82,$E82)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <f>'Original Data'!$B$84</f>
+        <v/>
+      </c>
+      <c r="B83" s="20">
+        <f>'Original Data'!$C$84*12</f>
+        <v/>
+      </c>
+      <c r="C83" s="20">
+        <f>'Original Data'!$O$84*12</f>
+        <v/>
+      </c>
+      <c r="D83" s="20">
+        <f>'Original Data'!$AA$84*12</f>
+        <v/>
+      </c>
+      <c r="E83" s="20">
+        <f>'Original Data'!$AM$84*12</f>
+        <v/>
+      </c>
+      <c r="F83">
+        <f>IF($E83&gt;10,RANK($E83,$E$3:$E$102,0)+COUNTIF($E$3:$E83,$E83)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <f>'Original Data'!$B$85</f>
+        <v/>
+      </c>
+      <c r="B84" s="20">
+        <f>'Original Data'!$C$85*12</f>
+        <v/>
+      </c>
+      <c r="C84" s="20">
+        <f>'Original Data'!$O$85*12</f>
+        <v/>
+      </c>
+      <c r="D84" s="20">
+        <f>'Original Data'!$AA$85*12</f>
+        <v/>
+      </c>
+      <c r="E84" s="20">
+        <f>'Original Data'!$AM$85*12</f>
+        <v/>
+      </c>
+      <c r="F84">
+        <f>IF($E84&gt;10,RANK($E84,$E$3:$E$102,0)+COUNTIF($E$3:$E84,$E84)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <f>'Original Data'!$B$86</f>
+        <v/>
+      </c>
+      <c r="B85" s="20">
+        <f>'Original Data'!$C$86*12</f>
+        <v/>
+      </c>
+      <c r="C85" s="20">
+        <f>'Original Data'!$O$86*12</f>
+        <v/>
+      </c>
+      <c r="D85" s="20">
+        <f>'Original Data'!$AA$86*12</f>
+        <v/>
+      </c>
+      <c r="E85" s="20">
+        <f>'Original Data'!$AM$86*12</f>
+        <v/>
+      </c>
+      <c r="F85">
+        <f>IF($E85&gt;10,RANK($E85,$E$3:$E$102,0)+COUNTIF($E$3:$E85,$E85)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <f>'Original Data'!$B$87</f>
+        <v/>
+      </c>
+      <c r="B86" s="20">
+        <f>'Original Data'!$C$87*12</f>
+        <v/>
+      </c>
+      <c r="C86" s="20">
+        <f>'Original Data'!$O$87*12</f>
+        <v/>
+      </c>
+      <c r="D86" s="20">
+        <f>'Original Data'!$AA$87*12</f>
+        <v/>
+      </c>
+      <c r="E86" s="20">
+        <f>'Original Data'!$AM$87*12</f>
+        <v/>
+      </c>
+      <c r="F86">
+        <f>IF($E86&gt;10,RANK($E86,$E$3:$E$102,0)+COUNTIF($E$3:$E86,$E86)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <f>'Original Data'!$B$88</f>
+        <v/>
+      </c>
+      <c r="B87" s="20">
+        <f>'Original Data'!$C$88*12</f>
+        <v/>
+      </c>
+      <c r="C87" s="20">
+        <f>'Original Data'!$O$88*12</f>
+        <v/>
+      </c>
+      <c r="D87" s="20">
+        <f>'Original Data'!$AA$88*12</f>
+        <v/>
+      </c>
+      <c r="E87" s="20">
+        <f>'Original Data'!$AM$88*12</f>
+        <v/>
+      </c>
+      <c r="F87">
+        <f>IF($E87&gt;10,RANK($E87,$E$3:$E$102,0)+COUNTIF($E$3:$E87,$E87)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <f>'Original Data'!$B$89</f>
+        <v/>
+      </c>
+      <c r="B88" s="20">
+        <f>'Original Data'!$C$89*12</f>
+        <v/>
+      </c>
+      <c r="C88" s="20">
+        <f>'Original Data'!$O$89*12</f>
+        <v/>
+      </c>
+      <c r="D88" s="20">
+        <f>'Original Data'!$AA$89*12</f>
+        <v/>
+      </c>
+      <c r="E88" s="20">
+        <f>'Original Data'!$AM$89*12</f>
+        <v/>
+      </c>
+      <c r="F88">
+        <f>IF($E88&gt;10,RANK($E88,$E$3:$E$102,0)+COUNTIF($E$3:$E88,$E88)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>'Original Data'!$B$90</f>
+        <v/>
+      </c>
+      <c r="B89" s="20">
+        <f>'Original Data'!$C$90*12</f>
+        <v/>
+      </c>
+      <c r="C89" s="20">
+        <f>'Original Data'!$O$90*12</f>
+        <v/>
+      </c>
+      <c r="D89" s="20">
+        <f>'Original Data'!$AA$90*12</f>
+        <v/>
+      </c>
+      <c r="E89" s="20">
+        <f>'Original Data'!$AM$90*12</f>
+        <v/>
+      </c>
+      <c r="F89">
+        <f>IF($E89&gt;10,RANK($E89,$E$3:$E$102,0)+COUNTIF($E$3:$E89,$E89)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <f>'Original Data'!$B$91</f>
+        <v/>
+      </c>
+      <c r="B90" s="20">
+        <f>'Original Data'!$C$91*12</f>
+        <v/>
+      </c>
+      <c r="C90" s="20">
+        <f>'Original Data'!$O$91*12</f>
+        <v/>
+      </c>
+      <c r="D90" s="20">
+        <f>'Original Data'!$AA$91*12</f>
+        <v/>
+      </c>
+      <c r="E90" s="20">
+        <f>'Original Data'!$AM$91*12</f>
+        <v/>
+      </c>
+      <c r="F90">
+        <f>IF($E90&gt;10,RANK($E90,$E$3:$E$102,0)+COUNTIF($E$3:$E90,$E90)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <f>'Original Data'!$B$92</f>
+        <v/>
+      </c>
+      <c r="B91" s="20">
+        <f>'Original Data'!$C$92*12</f>
+        <v/>
+      </c>
+      <c r="C91" s="20">
+        <f>'Original Data'!$O$92*12</f>
+        <v/>
+      </c>
+      <c r="D91" s="20">
+        <f>'Original Data'!$AA$92*12</f>
+        <v/>
+      </c>
+      <c r="E91" s="20">
+        <f>'Original Data'!$AM$92*12</f>
+        <v/>
+      </c>
+      <c r="F91">
+        <f>IF($E91&gt;10,RANK($E91,$E$3:$E$102,0)+COUNTIF($E$3:$E91,$E91)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <f>'Original Data'!$B$93</f>
+        <v/>
+      </c>
+      <c r="B92" s="20">
+        <f>'Original Data'!$C$93*12</f>
+        <v/>
+      </c>
+      <c r="C92" s="20">
+        <f>'Original Data'!$O$93*12</f>
+        <v/>
+      </c>
+      <c r="D92" s="20">
+        <f>'Original Data'!$AA$93*12</f>
+        <v/>
+      </c>
+      <c r="E92" s="20">
+        <f>'Original Data'!$AM$93*12</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>IF($E92&gt;10,RANK($E92,$E$3:$E$102,0)+COUNTIF($E$3:$E92,$E92)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <f>'Original Data'!$B$94</f>
+        <v/>
+      </c>
+      <c r="B93" s="20">
+        <f>'Original Data'!$C$94*12</f>
+        <v/>
+      </c>
+      <c r="C93" s="20">
+        <f>'Original Data'!$O$94*12</f>
+        <v/>
+      </c>
+      <c r="D93" s="20">
+        <f>'Original Data'!$AA$94*12</f>
+        <v/>
+      </c>
+      <c r="E93" s="20">
+        <f>'Original Data'!$AM$94*12</f>
+        <v/>
+      </c>
+      <c r="F93">
+        <f>IF($E93&gt;10,RANK($E93,$E$3:$E$102,0)+COUNTIF($E$3:$E93,$E93)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <f>'Original Data'!$B$95</f>
+        <v/>
+      </c>
+      <c r="B94" s="20">
+        <f>'Original Data'!$C$95*12</f>
+        <v/>
+      </c>
+      <c r="C94" s="20">
+        <f>'Original Data'!$O$95*12</f>
+        <v/>
+      </c>
+      <c r="D94" s="20">
+        <f>'Original Data'!$AA$95*12</f>
+        <v/>
+      </c>
+      <c r="E94" s="20">
+        <f>'Original Data'!$AM$95*12</f>
+        <v/>
+      </c>
+      <c r="F94">
+        <f>IF($E94&gt;10,RANK($E94,$E$3:$E$102,0)+COUNTIF($E$3:$E94,$E94)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <f>'Original Data'!$B$96</f>
+        <v/>
+      </c>
+      <c r="B95" s="20">
+        <f>'Original Data'!$C$96*12</f>
+        <v/>
+      </c>
+      <c r="C95" s="20">
+        <f>'Original Data'!$O$96*12</f>
+        <v/>
+      </c>
+      <c r="D95" s="20">
+        <f>'Original Data'!$AA$96*12</f>
+        <v/>
+      </c>
+      <c r="E95" s="20">
+        <f>'Original Data'!$AM$96*12</f>
+        <v/>
+      </c>
+      <c r="F95">
+        <f>IF($E95&gt;10,RANK($E95,$E$3:$E$102,0)+COUNTIF($E$3:$E95,$E95)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <f>'Original Data'!$B$97</f>
+        <v/>
+      </c>
+      <c r="B96" s="20">
+        <f>'Original Data'!$C$97*12</f>
+        <v/>
+      </c>
+      <c r="C96" s="20">
+        <f>'Original Data'!$O$97*12</f>
+        <v/>
+      </c>
+      <c r="D96" s="20">
+        <f>'Original Data'!$AA$97*12</f>
+        <v/>
+      </c>
+      <c r="E96" s="20">
+        <f>'Original Data'!$AM$97*12</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>IF($E96&gt;10,RANK($E96,$E$3:$E$102,0)+COUNTIF($E$3:$E96,$E96)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <f>'Original Data'!$B$98</f>
+        <v/>
+      </c>
+      <c r="B97" s="20">
+        <f>'Original Data'!$C$98*12</f>
+        <v/>
+      </c>
+      <c r="C97" s="20">
+        <f>'Original Data'!$O$98*12</f>
+        <v/>
+      </c>
+      <c r="D97" s="20">
+        <f>'Original Data'!$AA$98*12</f>
+        <v/>
+      </c>
+      <c r="E97" s="20">
+        <f>'Original Data'!$AM$98*12</f>
+        <v/>
+      </c>
+      <c r="F97">
+        <f>IF($E97&gt;10,RANK($E97,$E$3:$E$102,0)+COUNTIF($E$3:$E97,$E97)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <f>'Original Data'!$B$99</f>
+        <v/>
+      </c>
+      <c r="B98" s="20">
+        <f>'Original Data'!$C$99*12</f>
+        <v/>
+      </c>
+      <c r="C98" s="20">
+        <f>'Original Data'!$O$99*12</f>
+        <v/>
+      </c>
+      <c r="D98" s="20">
+        <f>'Original Data'!$AA$99*12</f>
+        <v/>
+      </c>
+      <c r="E98" s="20">
+        <f>'Original Data'!$AM$99*12</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF($E98&gt;10,RANK($E98,$E$3:$E$102,0)+COUNTIF($E$3:$E98,$E98)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <f>'Original Data'!$B$100</f>
+        <v/>
+      </c>
+      <c r="B99" s="20">
+        <f>'Original Data'!$C$100*12</f>
+        <v/>
+      </c>
+      <c r="C99" s="20">
+        <f>'Original Data'!$O$100*12</f>
+        <v/>
+      </c>
+      <c r="D99" s="20">
+        <f>'Original Data'!$AA$100*12</f>
+        <v/>
+      </c>
+      <c r="E99" s="20">
+        <f>'Original Data'!$AM$100*12</f>
+        <v/>
+      </c>
+      <c r="F99">
+        <f>IF($E99&gt;10,RANK($E99,$E$3:$E$102,0)+COUNTIF($E$3:$E99,$E99)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <f>'Original Data'!$B$101</f>
+        <v/>
+      </c>
+      <c r="B100" s="20">
+        <f>'Original Data'!$C$101*12</f>
+        <v/>
+      </c>
+      <c r="C100" s="20">
+        <f>'Original Data'!$O$101*12</f>
+        <v/>
+      </c>
+      <c r="D100" s="20">
+        <f>'Original Data'!$AA$101*12</f>
+        <v/>
+      </c>
+      <c r="E100" s="20">
+        <f>'Original Data'!$AM$101*12</f>
+        <v/>
+      </c>
+      <c r="F100">
+        <f>IF($E100&gt;10,RANK($E100,$E$3:$E$102,0)+COUNTIF($E$3:$E100,$E100)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <f>'Original Data'!$B$102</f>
+        <v/>
+      </c>
+      <c r="B101" s="20">
+        <f>'Original Data'!$C$102*12</f>
+        <v/>
+      </c>
+      <c r="C101" s="20">
+        <f>'Original Data'!$O$102*12</f>
+        <v/>
+      </c>
+      <c r="D101" s="20">
+        <f>'Original Data'!$AA$102*12</f>
+        <v/>
+      </c>
+      <c r="E101" s="20">
+        <f>'Original Data'!$AM$102*12</f>
+        <v/>
+      </c>
+      <c r="F101">
+        <f>IF($E101&gt;10,RANK($E101,$E$3:$E$102,0)+COUNTIF($E$3:$E101,$E101)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <f>'Original Data'!$B$103</f>
+        <v/>
+      </c>
+      <c r="B102" s="20">
+        <f>'Original Data'!$C$103*12</f>
+        <v/>
+      </c>
+      <c r="C102" s="20">
+        <f>'Original Data'!$O$103*12</f>
+        <v/>
+      </c>
+      <c r="D102" s="20">
+        <f>'Original Data'!$AA$103*12</f>
+        <v/>
+      </c>
+      <c r="E102" s="20">
+        <f>'Original Data'!$AM$103*12</f>
+        <v/>
+      </c>
+      <c r="F102">
+        <f>IF($E102&gt;10,RANK($E102,$E$3:$E$102,0)+COUNTIF($E$3:$E102,$E102)-1,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>Annual Waterfall Aggregates</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Dec-22</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Dec-23</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Dec-24</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>Dec-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>BoP ARR</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="n"/>
+      <c r="C105" s="20">
+        <f>SUM($B$3:$B$102)</f>
+        <v/>
+      </c>
+      <c r="D105" s="20">
+        <f>SUM($C$3:$C$102)</f>
+        <v/>
+      </c>
+      <c r="E105" s="20">
+        <f>SUM($D$3:$D$102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="n"/>
+      <c r="C106" s="20">
+        <f>SUMPRODUCT(($B$3:$B$102&lt;=0)*($C$3:$C$102&gt;0)*$C$3:$C$102)</f>
+        <v/>
+      </c>
+      <c r="D106" s="20">
+        <f>SUMPRODUCT(($C$3:$C$102&lt;=0)*($D$3:$D$102&gt;0)*$D$3:$D$102)</f>
+        <v/>
+      </c>
+      <c r="E106" s="20">
+        <f>SUMPRODUCT(($D$3:$D$102&lt;=0)*($E$3:$E$102&gt;0)*$E$3:$E$102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Upsell</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="n"/>
+      <c r="C107" s="20">
+        <f>SUMPRODUCT(($B$3:$B$102&gt;0)*($C$3:$C$102&gt;0)*($C$3:$C$102&gt;$B$3:$B$102)*($C$3:$C$102-$B$3:$B$102))</f>
+        <v/>
+      </c>
+      <c r="D107" s="20">
+        <f>SUMPRODUCT(($C$3:$C$102&gt;0)*($D$3:$D$102&gt;0)*($D$3:$D$102&gt;$C$3:$C$102)*($D$3:$D$102-$C$3:$C$102))</f>
+        <v/>
+      </c>
+      <c r="E107" s="20">
+        <f>SUMPRODUCT(($D$3:$D$102&gt;0)*($E$3:$E$102&gt;0)*($E$3:$E$102&gt;$D$3:$D$102)*($E$3:$E$102-$D$3:$D$102))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>(Downsell)</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="n"/>
+      <c r="C108" s="20">
+        <f>SUMPRODUCT(($B$3:$B$102&gt;0)*($C$3:$C$102&gt;0)*($C$3:$C$102&lt;$B$3:$B$102)*($C$3:$C$102-$B$3:$B$102))</f>
+        <v/>
+      </c>
+      <c r="D108" s="20">
+        <f>SUMPRODUCT(($C$3:$C$102&gt;0)*($D$3:$D$102&gt;0)*($D$3:$D$102&lt;$C$3:$C$102)*($D$3:$D$102-$C$3:$C$102))</f>
+        <v/>
+      </c>
+      <c r="E108" s="20">
+        <f>SUMPRODUCT(($D$3:$D$102&gt;0)*($E$3:$E$102&gt;0)*($E$3:$E$102&lt;$D$3:$D$102)*($E$3:$E$102-$D$3:$D$102))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>(Churn)</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="n"/>
+      <c r="C109" s="20">
+        <f>-SUMPRODUCT(($B$3:$B$102&gt;0)*($C$3:$C$102&lt;=0)*$B$3:$B$102)</f>
+        <v/>
+      </c>
+      <c r="D109" s="20">
+        <f>-SUMPRODUCT(($C$3:$C$102&gt;0)*($D$3:$D$102&lt;=0)*$C$3:$C$102)</f>
+        <v/>
+      </c>
+      <c r="E109" s="20">
+        <f>-SUMPRODUCT(($D$3:$D$102&gt;0)*($E$3:$E$102&lt;=0)*$D$3:$D$102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EoP ARR</t>
+        </is>
+      </c>
+      <c r="B110" s="20">
+        <f>SUM($B$3:$B$102)</f>
+        <v/>
+      </c>
+      <c r="C110" s="20">
+        <f>SUM($C$3:$C$102)</f>
+        <v/>
+      </c>
+      <c r="D110" s="20">
+        <f>SUM($D$3:$D$102)</f>
+        <v/>
+      </c>
+      <c r="E110" s="20">
+        <f>SUM($E$3:$E$102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BoP Customers</t>
+        </is>
+      </c>
+      <c r="C112">
+        <f>COUNTIF($B$3:$B$102,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D112">
+        <f>COUNTIF($C$3:$C$102,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E112">
+        <f>COUNTIF($D$3:$D$102,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C113">
+        <f>SUMPRODUCT(($B$3:$B$102&lt;=0)*($C$3:$C$102&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="D113">
+        <f>SUMPRODUCT(($C$3:$C$102&lt;=0)*($D$3:$D$102&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="E113">
+        <f>SUMPRODUCT(($D$3:$D$102&lt;=0)*($E$3:$E$102&gt;0)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>(Churn)</t>
+        </is>
+      </c>
+      <c r="C114">
+        <f>SUMPRODUCT(($B$3:$B$102&gt;0)*($C$3:$C$102&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="D114">
+        <f>SUMPRODUCT(($C$3:$C$102&gt;0)*($D$3:$D$102&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="E114">
+        <f>SUMPRODUCT(($D$3:$D$102&gt;0)*($E$3:$E$102&lt;=0)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EoP Customers</t>
+        </is>
+      </c>
+      <c r="B115">
+        <f>COUNTIF($B$3:$B$102,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="C115">
+        <f>COUNTIF($C$3:$C$102,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D115">
+        <f>COUNTIF($D$3:$D$102,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E115">
+        <f>COUNTIF($E$3:$E$102,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly Waterfall Aggregates</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Q4-22</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Q1-23</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Q2-23</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Q3-23</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Q4-23</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Q1-24</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Q2-24</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>Q3-24</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>Q4-24</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>Q1-25</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>Q2-25</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Q3-25</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
+          <t>Q4-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>BoP ARR</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="n"/>
+      <c r="C118" s="20">
+        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <v/>
+      </c>
+      <c r="D118" s="20">
+        <f>SUM('Original Data'!$F$4:$F$103)*12</f>
+        <v/>
+      </c>
+      <c r="E118" s="20">
+        <f>SUM('Original Data'!$I$4:$I$103)*12</f>
+        <v/>
+      </c>
+      <c r="F118" s="20">
+        <f>SUM('Original Data'!$L$4:$L$103)*12</f>
+        <v/>
+      </c>
+      <c r="G118" s="20">
+        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <v/>
+      </c>
+      <c r="H118" s="20">
+        <f>SUM('Original Data'!$R$4:$R$103)*12</f>
+        <v/>
+      </c>
+      <c r="I118" s="20">
+        <f>SUM('Original Data'!$U$4:$U$103)*12</f>
+        <v/>
+      </c>
+      <c r="J118" s="20">
+        <f>SUM('Original Data'!$X$4:$X$103)*12</f>
+        <v/>
+      </c>
+      <c r="K118" s="20">
+        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <v/>
+      </c>
+      <c r="L118" s="20">
+        <f>SUM('Original Data'!$AD$4:$AD$103)*12</f>
+        <v/>
+      </c>
+      <c r="M118" s="20">
+        <f>SUM('Original Data'!$AG$4:$AG$103)*12</f>
+        <v/>
+      </c>
+      <c r="N118" s="20">
+        <f>SUM('Original Data'!$AJ$4:$AJ$103)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B119" s="20" t="n"/>
+      <c r="C119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$F$4:$F$103&gt;0)*'Original Data'!$F$4:$F$103)*12</f>
+        <v/>
+      </c>
+      <c r="D119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&lt;=0)*('Original Data'!$I$4:$I$103&gt;0)*'Original Data'!$I$4:$I$103)*12</f>
+        <v/>
+      </c>
+      <c r="E119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&lt;=0)*('Original Data'!$L$4:$L$103&gt;0)*'Original Data'!$L$4:$L$103)*12</f>
+        <v/>
+      </c>
+      <c r="F119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*'Original Data'!$O$4:$O$103)*12</f>
+        <v/>
+      </c>
+      <c r="G119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$R$4:$R$103&gt;0)*'Original Data'!$R$4:$R$103)*12</f>
+        <v/>
+      </c>
+      <c r="H119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&lt;=0)*('Original Data'!$U$4:$U$103&gt;0)*'Original Data'!$U$4:$U$103)*12</f>
+        <v/>
+      </c>
+      <c r="I119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&lt;=0)*('Original Data'!$X$4:$X$103&gt;0)*'Original Data'!$X$4:$X$103)*12</f>
+        <v/>
+      </c>
+      <c r="J119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <v/>
+      </c>
+      <c r="K119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AD$4:$AD$103&gt;0)*'Original Data'!$AD$4:$AD$103)*12</f>
+        <v/>
+      </c>
+      <c r="L119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&lt;=0)*('Original Data'!$AG$4:$AG$103&gt;0)*'Original Data'!$AG$4:$AG$103)*12</f>
+        <v/>
+      </c>
+      <c r="M119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&lt;=0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*'Original Data'!$AJ$4:$AJ$103)*12</f>
+        <v/>
+      </c>
+      <c r="N119" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*'Original Data'!$AM$4:$AM$103)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Upsell</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="n"/>
+      <c r="C120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$F$4:$F$103&gt;'Original Data'!$C$4:$C$103)*('Original Data'!$F$4:$F$103-'Original Data'!$C$4:$C$103))*12</f>
+        <v/>
+      </c>
+      <c r="D120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$I$4:$I$103&gt;'Original Data'!$F$4:$F$103)*('Original Data'!$I$4:$I$103-'Original Data'!$F$4:$F$103))*12</f>
+        <v/>
+      </c>
+      <c r="E120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$L$4:$L$103&gt;'Original Data'!$I$4:$I$103)*('Original Data'!$L$4:$L$103-'Original Data'!$I$4:$I$103))*12</f>
+        <v/>
+      </c>
+      <c r="F120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&gt;'Original Data'!$L$4:$L$103)*('Original Data'!$O$4:$O$103-'Original Data'!$L$4:$L$103))*12</f>
+        <v/>
+      </c>
+      <c r="G120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$R$4:$R$103&gt;'Original Data'!$O$4:$O$103)*('Original Data'!$R$4:$R$103-'Original Data'!$O$4:$O$103))*12</f>
+        <v/>
+      </c>
+      <c r="H120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$U$4:$U$103&gt;'Original Data'!$R$4:$R$103)*('Original Data'!$U$4:$U$103-'Original Data'!$R$4:$R$103))*12</f>
+        <v/>
+      </c>
+      <c r="I120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$X$4:$X$103&gt;'Original Data'!$U$4:$U$103)*('Original Data'!$X$4:$X$103-'Original Data'!$U$4:$U$103))*12</f>
+        <v/>
+      </c>
+      <c r="J120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;'Original Data'!$X$4:$X$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$X$4:$X$103))*12</f>
+        <v/>
+      </c>
+      <c r="K120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AD$4:$AD$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <v/>
+      </c>
+      <c r="L120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;'Original Data'!$AD$4:$AD$103)*('Original Data'!$AG$4:$AG$103-'Original Data'!$AD$4:$AD$103))*12</f>
+        <v/>
+      </c>
+      <c r="M120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;'Original Data'!$AG$4:$AG$103)*('Original Data'!$AJ$4:$AJ$103-'Original Data'!$AG$4:$AG$103))*12</f>
+        <v/>
+      </c>
+      <c r="N120" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;'Original Data'!$AJ$4:$AJ$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AJ$4:$AJ$103))*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>(Downsell)</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="n"/>
+      <c r="C121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$F$4:$F$103&lt;'Original Data'!$C$4:$C$103)*('Original Data'!$F$4:$F$103-'Original Data'!$C$4:$C$103))*12</f>
+        <v/>
+      </c>
+      <c r="D121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$I$4:$I$103&lt;'Original Data'!$F$4:$F$103)*('Original Data'!$I$4:$I$103-'Original Data'!$F$4:$F$103))*12</f>
+        <v/>
+      </c>
+      <c r="E121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$L$4:$L$103&lt;'Original Data'!$I$4:$I$103)*('Original Data'!$L$4:$L$103-'Original Data'!$I$4:$I$103))*12</f>
+        <v/>
+      </c>
+      <c r="F121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&lt;'Original Data'!$L$4:$L$103)*('Original Data'!$O$4:$O$103-'Original Data'!$L$4:$L$103))*12</f>
+        <v/>
+      </c>
+      <c r="G121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$R$4:$R$103&lt;'Original Data'!$O$4:$O$103)*('Original Data'!$R$4:$R$103-'Original Data'!$O$4:$O$103))*12</f>
+        <v/>
+      </c>
+      <c r="H121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$U$4:$U$103&lt;'Original Data'!$R$4:$R$103)*('Original Data'!$U$4:$U$103-'Original Data'!$R$4:$R$103))*12</f>
+        <v/>
+      </c>
+      <c r="I121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$X$4:$X$103&lt;'Original Data'!$U$4:$U$103)*('Original Data'!$X$4:$X$103-'Original Data'!$U$4:$U$103))*12</f>
+        <v/>
+      </c>
+      <c r="J121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;'Original Data'!$X$4:$X$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$X$4:$X$103))*12</f>
+        <v/>
+      </c>
+      <c r="K121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AD$4:$AD$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <v/>
+      </c>
+      <c r="L121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;'Original Data'!$AD$4:$AD$103)*('Original Data'!$AG$4:$AG$103-'Original Data'!$AD$4:$AD$103))*12</f>
+        <v/>
+      </c>
+      <c r="M121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;'Original Data'!$AG$4:$AG$103)*('Original Data'!$AJ$4:$AJ$103-'Original Data'!$AG$4:$AG$103))*12</f>
+        <v/>
+      </c>
+      <c r="N121" s="20">
+        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;'Original Data'!$AJ$4:$AJ$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AJ$4:$AJ$103))*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>(Churn)</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="n"/>
+      <c r="C122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&lt;=0)*'Original Data'!$C$4:$C$103)*12</f>
+        <v/>
+      </c>
+      <c r="D122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&lt;=0)*'Original Data'!$F$4:$F$103)*12</f>
+        <v/>
+      </c>
+      <c r="E122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&lt;=0)*'Original Data'!$I$4:$I$103)*12</f>
+        <v/>
+      </c>
+      <c r="F122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*'Original Data'!$L$4:$L$103)*12</f>
+        <v/>
+      </c>
+      <c r="G122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&lt;=0)*'Original Data'!$O$4:$O$103)*12</f>
+        <v/>
+      </c>
+      <c r="H122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&lt;=0)*'Original Data'!$R$4:$R$103)*12</f>
+        <v/>
+      </c>
+      <c r="I122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&lt;=0)*'Original Data'!$U$4:$U$103)*12</f>
+        <v/>
+      </c>
+      <c r="J122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*'Original Data'!$X$4:$X$103)*12</f>
+        <v/>
+      </c>
+      <c r="K122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;=0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <v/>
+      </c>
+      <c r="L122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;=0)*'Original Data'!$AD$4:$AD$103)*12</f>
+        <v/>
+      </c>
+      <c r="M122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;=0)*'Original Data'!$AG$4:$AG$103)*12</f>
+        <v/>
+      </c>
+      <c r="N122" s="20">
+        <f>-SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*'Original Data'!$AJ$4:$AJ$103)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>EoP ARR</t>
+        </is>
+      </c>
+      <c r="B123" s="20">
+        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <v/>
+      </c>
+      <c r="C123" s="20">
+        <f>SUM('Original Data'!$F$4:$F$103)*12</f>
+        <v/>
+      </c>
+      <c r="D123" s="20">
+        <f>SUM('Original Data'!$I$4:$I$103)*12</f>
+        <v/>
+      </c>
+      <c r="E123" s="20">
+        <f>SUM('Original Data'!$L$4:$L$103)*12</f>
+        <v/>
+      </c>
+      <c r="F123" s="20">
+        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <v/>
+      </c>
+      <c r="G123" s="20">
+        <f>SUM('Original Data'!$R$4:$R$103)*12</f>
+        <v/>
+      </c>
+      <c r="H123" s="20">
+        <f>SUM('Original Data'!$U$4:$U$103)*12</f>
+        <v/>
+      </c>
+      <c r="I123" s="20">
+        <f>SUM('Original Data'!$X$4:$X$103)*12</f>
+        <v/>
+      </c>
+      <c r="J123" s="20">
+        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <v/>
+      </c>
+      <c r="K123" s="20">
+        <f>SUM('Original Data'!$AD$4:$AD$103)*12</f>
+        <v/>
+      </c>
+      <c r="L123" s="20">
+        <f>SUM('Original Data'!$AG$4:$AG$103)*12</f>
+        <v/>
+      </c>
+      <c r="M123" s="20">
+        <f>SUM('Original Data'!$AJ$4:$AJ$103)*12</f>
+        <v/>
+      </c>
+      <c r="N123" s="20">
+        <f>SUM('Original Data'!$AM$4:$AM$103)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BoP Customers</t>
+        </is>
+      </c>
+      <c r="C125">
+        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D125">
+        <f>COUNTIF('Original Data'!$F$4:$F$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E125">
+        <f>COUNTIF('Original Data'!$I$4:$I$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="F125">
+        <f>COUNTIF('Original Data'!$L$4:$L$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="G125">
+        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H125">
+        <f>COUNTIF('Original Data'!$R$4:$R$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="I125">
+        <f>COUNTIF('Original Data'!$U$4:$U$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="J125">
+        <f>COUNTIF('Original Data'!$X$4:$X$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="K125">
+        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="L125">
+        <f>COUNTIF('Original Data'!$AD$4:$AD$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="M125">
+        <f>COUNTIF('Original Data'!$AG$4:$AG$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="N125">
+        <f>COUNTIF('Original Data'!$AJ$4:$AJ$103,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C126">
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$F$4:$F$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="D126">
+        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&lt;=0)*('Original Data'!$I$4:$I$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="E126">
+        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&lt;=0)*('Original Data'!$L$4:$L$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="F126">
+        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="G126">
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$R$4:$R$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="H126">
+        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&lt;=0)*('Original Data'!$U$4:$U$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="I126">
+        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&lt;=0)*('Original Data'!$X$4:$X$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="J126">
+        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="K126">
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AD$4:$AD$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="L126">
+        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&lt;=0)*('Original Data'!$AG$4:$AG$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="M126">
+        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&lt;=0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*1)</f>
+        <v/>
+      </c>
+      <c r="N126">
+        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>(Churn)</t>
+        </is>
+      </c>
+      <c r="C127">
+        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="D127">
+        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="F127">
+        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="G127">
+        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="H127">
+        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="I127">
+        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="J127">
+        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="K127">
+        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="L127">
+        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="M127">
+        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+      <c r="N127">
+        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EoP Customers</t>
+        </is>
+      </c>
+      <c r="B128">
+        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="C128">
+        <f>COUNTIF('Original Data'!$F$4:$F$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D128">
+        <f>COUNTIF('Original Data'!$I$4:$I$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E128">
+        <f>COUNTIF('Original Data'!$L$4:$L$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="F128">
+        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="G128">
+        <f>COUNTIF('Original Data'!$R$4:$R$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H128">
+        <f>COUNTIF('Original Data'!$U$4:$U$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="I128">
+        <f>COUNTIF('Original Data'!$X$4:$X$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="J128">
+        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="K128">
+        <f>COUNTIF('Original Data'!$AD$4:$AD$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="L128">
+        <f>COUNTIF('Original Data'!$AG$4:$AG$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="M128">
+        <f>COUNTIF('Original Data'!$AJ$4:$AJ$103,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="N128">
+        <f>COUNTIF('Original Data'!$AM$4:$AM$103,"&gt;0")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1239,51 +4780,51 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$C$118</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>SUM('Original Data'!$F$4:$F$103)*12</f>
+        <f>'Intermediate Calcs'!$D$118</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>SUM('Original Data'!$I$4:$I$103)*12</f>
+        <f>'Intermediate Calcs'!$E$118</f>
         <v/>
       </c>
       <c r="F3" s="6">
-        <f>SUM('Original Data'!$L$4:$L$103)*12</f>
+        <f>'Intermediate Calcs'!$F$118</f>
         <v/>
       </c>
       <c r="G3" s="6">
-        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$G$118</f>
         <v/>
       </c>
       <c r="H3" s="6">
-        <f>SUM('Original Data'!$R$4:$R$103)*12</f>
+        <f>'Intermediate Calcs'!$H$118</f>
         <v/>
       </c>
       <c r="I3" s="6">
-        <f>SUM('Original Data'!$U$4:$U$103)*12</f>
+        <f>'Intermediate Calcs'!$I$118</f>
         <v/>
       </c>
       <c r="J3" s="6">
-        <f>SUM('Original Data'!$X$4:$X$103)*12</f>
+        <f>'Intermediate Calcs'!$J$118</f>
         <v/>
       </c>
       <c r="K3" s="6">
-        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$K$118</f>
         <v/>
       </c>
       <c r="L3" s="6">
-        <f>SUM('Original Data'!$AD$4:$AD$103)*12</f>
+        <f>'Intermediate Calcs'!$L$118</f>
         <v/>
       </c>
       <c r="M3" s="6">
-        <f>SUM('Original Data'!$AG$4:$AG$103)*12</f>
+        <f>'Intermediate Calcs'!$M$118</f>
         <v/>
       </c>
       <c r="N3" s="6">
-        <f>SUM('Original Data'!$AJ$4:$AJ$103)*12</f>
+        <f>'Intermediate Calcs'!$N$118</f>
         <v/>
       </c>
     </row>
@@ -1295,51 +4836,51 @@
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$F$4:$F$103&gt;0)*'Original Data'!$F$4:$F$103)*12</f>
+        <f>'Intermediate Calcs'!$C$119</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&lt;=0)*('Original Data'!$I$4:$I$103&gt;0)*'Original Data'!$I$4:$I$103)*12</f>
+        <f>'Intermediate Calcs'!$D$119</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&lt;=0)*('Original Data'!$L$4:$L$103&gt;0)*'Original Data'!$L$4:$L$103)*12</f>
+        <f>'Intermediate Calcs'!$E$119</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*'Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$F$119</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$R$4:$R$103&gt;0)*'Original Data'!$R$4:$R$103)*12</f>
+        <f>'Intermediate Calcs'!$G$119</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&lt;=0)*('Original Data'!$U$4:$U$103&gt;0)*'Original Data'!$U$4:$U$103)*12</f>
+        <f>'Intermediate Calcs'!$H$119</f>
         <v/>
       </c>
       <c r="I4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&lt;=0)*('Original Data'!$X$4:$X$103&gt;0)*'Original Data'!$X$4:$X$103)*12</f>
+        <f>'Intermediate Calcs'!$I$119</f>
         <v/>
       </c>
       <c r="J4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$J$119</f>
         <v/>
       </c>
       <c r="K4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AD$4:$AD$103&gt;0)*'Original Data'!$AD$4:$AD$103)*12</f>
+        <f>'Intermediate Calcs'!$K$119</f>
         <v/>
       </c>
       <c r="L4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&lt;=0)*('Original Data'!$AG$4:$AG$103&gt;0)*'Original Data'!$AG$4:$AG$103)*12</f>
+        <f>'Intermediate Calcs'!$L$119</f>
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&lt;=0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*'Original Data'!$AJ$4:$AJ$103)*12</f>
+        <f>'Intermediate Calcs'!$M$119</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*'Original Data'!$AM$4:$AM$103)*12</f>
+        <f>'Intermediate Calcs'!$N$119</f>
         <v/>
       </c>
     </row>
@@ -1351,51 +4892,51 @@
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$F$4:$F$103&gt;'Original Data'!$C$4:$C$103)*('Original Data'!$F$4:$F$103-'Original Data'!$C$4:$C$103))*12</f>
+        <f>'Intermediate Calcs'!$C$120</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$I$4:$I$103&gt;'Original Data'!$F$4:$F$103)*('Original Data'!$I$4:$I$103-'Original Data'!$F$4:$F$103))*12</f>
+        <f>'Intermediate Calcs'!$D$120</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$L$4:$L$103&gt;'Original Data'!$I$4:$I$103)*('Original Data'!$L$4:$L$103-'Original Data'!$I$4:$I$103))*12</f>
+        <f>'Intermediate Calcs'!$E$120</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&gt;'Original Data'!$L$4:$L$103)*('Original Data'!$O$4:$O$103-'Original Data'!$L$4:$L$103))*12</f>
+        <f>'Intermediate Calcs'!$F$120</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$R$4:$R$103&gt;'Original Data'!$O$4:$O$103)*('Original Data'!$R$4:$R$103-'Original Data'!$O$4:$O$103))*12</f>
+        <f>'Intermediate Calcs'!$G$120</f>
         <v/>
       </c>
       <c r="H5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$U$4:$U$103&gt;'Original Data'!$R$4:$R$103)*('Original Data'!$U$4:$U$103-'Original Data'!$R$4:$R$103))*12</f>
+        <f>'Intermediate Calcs'!$H$120</f>
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$X$4:$X$103&gt;'Original Data'!$U$4:$U$103)*('Original Data'!$X$4:$X$103-'Original Data'!$U$4:$U$103))*12</f>
+        <f>'Intermediate Calcs'!$I$120</f>
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;'Original Data'!$X$4:$X$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$X$4:$X$103))*12</f>
+        <f>'Intermediate Calcs'!$J$120</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AD$4:$AD$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <f>'Intermediate Calcs'!$K$120</f>
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;'Original Data'!$AD$4:$AD$103)*('Original Data'!$AG$4:$AG$103-'Original Data'!$AD$4:$AD$103))*12</f>
+        <f>'Intermediate Calcs'!$L$120</f>
         <v/>
       </c>
       <c r="M5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;'Original Data'!$AG$4:$AG$103)*('Original Data'!$AJ$4:$AJ$103-'Original Data'!$AG$4:$AG$103))*12</f>
+        <f>'Intermediate Calcs'!$M$120</f>
         <v/>
       </c>
       <c r="N5" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;'Original Data'!$AJ$4:$AJ$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AJ$4:$AJ$103))*12</f>
+        <f>'Intermediate Calcs'!$N$120</f>
         <v/>
       </c>
     </row>
@@ -1407,51 +4948,51 @@
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$F$4:$F$103&lt;'Original Data'!$C$4:$C$103)*('Original Data'!$F$4:$F$103-'Original Data'!$C$4:$C$103))*12</f>
+        <f>'Intermediate Calcs'!$C$121</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$I$4:$I$103&lt;'Original Data'!$F$4:$F$103)*('Original Data'!$I$4:$I$103-'Original Data'!$F$4:$F$103))*12</f>
+        <f>'Intermediate Calcs'!$D$121</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$L$4:$L$103&lt;'Original Data'!$I$4:$I$103)*('Original Data'!$L$4:$L$103-'Original Data'!$I$4:$I$103))*12</f>
+        <f>'Intermediate Calcs'!$E$121</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$O$4:$O$103&lt;'Original Data'!$L$4:$L$103)*('Original Data'!$O$4:$O$103-'Original Data'!$L$4:$L$103))*12</f>
+        <f>'Intermediate Calcs'!$F$121</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$R$4:$R$103&lt;'Original Data'!$O$4:$O$103)*('Original Data'!$R$4:$R$103-'Original Data'!$O$4:$O$103))*12</f>
+        <f>'Intermediate Calcs'!$G$121</f>
         <v/>
       </c>
       <c r="H6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$U$4:$U$103&lt;'Original Data'!$R$4:$R$103)*('Original Data'!$U$4:$U$103-'Original Data'!$R$4:$R$103))*12</f>
+        <f>'Intermediate Calcs'!$H$121</f>
         <v/>
       </c>
       <c r="I6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$X$4:$X$103&lt;'Original Data'!$U$4:$U$103)*('Original Data'!$X$4:$X$103-'Original Data'!$U$4:$U$103))*12</f>
+        <f>'Intermediate Calcs'!$I$121</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;'Original Data'!$X$4:$X$103)*('Original Data'!$AA$4:$AA$103-'Original Data'!$X$4:$X$103))*12</f>
+        <f>'Intermediate Calcs'!$J$121</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;'Original Data'!$AA$4:$AA$103)*('Original Data'!$AD$4:$AD$103-'Original Data'!$AA$4:$AA$103))*12</f>
+        <f>'Intermediate Calcs'!$K$121</f>
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;'Original Data'!$AD$4:$AD$103)*('Original Data'!$AG$4:$AG$103-'Original Data'!$AD$4:$AD$103))*12</f>
+        <f>'Intermediate Calcs'!$L$121</f>
         <v/>
       </c>
       <c r="M6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;'Original Data'!$AG$4:$AG$103)*('Original Data'!$AJ$4:$AJ$103-'Original Data'!$AG$4:$AG$103))*12</f>
+        <f>'Intermediate Calcs'!$M$121</f>
         <v/>
       </c>
       <c r="N6" s="6">
-        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;'Original Data'!$AJ$4:$AJ$103)*('Original Data'!$AM$4:$AM$103-'Original Data'!$AJ$4:$AJ$103))*12</f>
+        <f>'Intermediate Calcs'!$N$121</f>
         <v/>
       </c>
     </row>
@@ -1463,51 +5004,51 @@
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&lt;=0)*'Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$C$122</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&lt;=0)*'Original Data'!$F$4:$F$103)*12</f>
+        <f>'Intermediate Calcs'!$D$122</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&lt;=0)*'Original Data'!$I$4:$I$103)*12</f>
+        <f>'Intermediate Calcs'!$E$122</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*'Original Data'!$L$4:$L$103)*12</f>
+        <f>'Intermediate Calcs'!$F$122</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&lt;=0)*'Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$G$122</f>
         <v/>
       </c>
       <c r="H7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&lt;=0)*'Original Data'!$R$4:$R$103)*12</f>
+        <f>'Intermediate Calcs'!$H$122</f>
         <v/>
       </c>
       <c r="I7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&lt;=0)*'Original Data'!$U$4:$U$103)*12</f>
+        <f>'Intermediate Calcs'!$I$122</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*'Original Data'!$X$4:$X$103)*12</f>
+        <f>'Intermediate Calcs'!$J$122</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;=0)*'Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$K$122</f>
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;=0)*'Original Data'!$AD$4:$AD$103)*12</f>
+        <f>'Intermediate Calcs'!$L$122</f>
         <v/>
       </c>
       <c r="M7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;=0)*'Original Data'!$AG$4:$AG$103)*12</f>
+        <f>'Intermediate Calcs'!$M$122</f>
         <v/>
       </c>
       <c r="N7" s="6">
-        <f>-SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*'Original Data'!$AJ$4:$AJ$103)*12</f>
+        <f>'Intermediate Calcs'!$N$122</f>
         <v/>
       </c>
     </row>
@@ -1518,55 +5059,55 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <f>'Intermediate Calcs'!$B$123</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>SUM('Original Data'!$F$4:$F$103)*12</f>
+        <f>'Intermediate Calcs'!$C$123</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>SUM('Original Data'!$I$4:$I$103)*12</f>
+        <f>'Intermediate Calcs'!$D$123</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>SUM('Original Data'!$L$4:$L$103)*12</f>
+        <f>'Intermediate Calcs'!$E$123</f>
         <v/>
       </c>
       <c r="F8" s="8">
-        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <f>'Intermediate Calcs'!$F$123</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>SUM('Original Data'!$R$4:$R$103)*12</f>
+        <f>'Intermediate Calcs'!$G$123</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>SUM('Original Data'!$U$4:$U$103)*12</f>
+        <f>'Intermediate Calcs'!$H$123</f>
         <v/>
       </c>
       <c r="I8" s="8">
-        <f>SUM('Original Data'!$X$4:$X$103)*12</f>
+        <f>'Intermediate Calcs'!$I$123</f>
         <v/>
       </c>
       <c r="J8" s="8">
-        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <f>'Intermediate Calcs'!$J$123</f>
         <v/>
       </c>
       <c r="K8" s="8">
-        <f>SUM('Original Data'!$AD$4:$AD$103)*12</f>
+        <f>'Intermediate Calcs'!$K$123</f>
         <v/>
       </c>
       <c r="L8" s="8">
-        <f>SUM('Original Data'!$AG$4:$AG$103)*12</f>
+        <f>'Intermediate Calcs'!$L$123</f>
         <v/>
       </c>
       <c r="M8" s="8">
-        <f>SUM('Original Data'!$AJ$4:$AJ$103)*12</f>
+        <f>'Intermediate Calcs'!$M$123</f>
         <v/>
       </c>
       <c r="N8" s="8">
-        <f>SUM('Original Data'!$AM$4:$AM$103)*12</f>
+        <f>'Intermediate Calcs'!$N$123</f>
         <v/>
       </c>
     </row>
@@ -2234,51 +5775,51 @@
       </c>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="16">
-        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$C$125</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>COUNTIF('Original Data'!$F$4:$F$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$D$125</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIF('Original Data'!$I$4:$I$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$E$125</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIF('Original Data'!$L$4:$L$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$F$125</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$G$125</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIF('Original Data'!$R$4:$R$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$H$125</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIF('Original Data'!$U$4:$U$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$I$125</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIF('Original Data'!$X$4:$X$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$J$125</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$K$125</f>
         <v/>
       </c>
       <c r="L22" s="16">
-        <f>COUNTIF('Original Data'!$AD$4:$AD$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$L$125</f>
         <v/>
       </c>
       <c r="M22" s="16">
-        <f>COUNTIF('Original Data'!$AG$4:$AG$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$M$125</f>
         <v/>
       </c>
       <c r="N22" s="16">
-        <f>COUNTIF('Original Data'!$AJ$4:$AJ$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$N$125</f>
         <v/>
       </c>
     </row>
@@ -2290,51 +5831,51 @@
       </c>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&lt;=0)*('Original Data'!$F$4:$F$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$C$126</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&lt;=0)*('Original Data'!$I$4:$I$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$D$126</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&lt;=0)*('Original Data'!$L$4:$L$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$E$126</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&lt;=0)*('Original Data'!$O$4:$O$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$F$126</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&lt;=0)*('Original Data'!$R$4:$R$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$G$126</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&lt;=0)*('Original Data'!$U$4:$U$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$H$126</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&lt;=0)*('Original Data'!$X$4:$X$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$I$126</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&lt;=0)*('Original Data'!$AA$4:$AA$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$J$126</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&lt;=0)*('Original Data'!$AD$4:$AD$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$K$126</f>
         <v/>
       </c>
       <c r="L23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&lt;=0)*('Original Data'!$AG$4:$AG$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$L$126</f>
         <v/>
       </c>
       <c r="M23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&lt;=0)*('Original Data'!$AJ$4:$AJ$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$M$126</f>
         <v/>
       </c>
       <c r="N23" s="16">
-        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&lt;=0)*('Original Data'!$AM$4:$AM$103&gt;0)*1)</f>
+        <f>'Intermediate Calcs'!$N$126</f>
         <v/>
       </c>
     </row>
@@ -2346,51 +5887,51 @@
       </c>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$C$4:$C$103&gt;0)*('Original Data'!$F$4:$F$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$C$127</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$F$4:$F$103&gt;0)*('Original Data'!$I$4:$I$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$D$127</f>
         <v/>
       </c>
       <c r="E24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$I$4:$I$103&gt;0)*('Original Data'!$L$4:$L$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$E$127</f>
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$L$4:$L$103&gt;0)*('Original Data'!$O$4:$O$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$F$127</f>
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$O$4:$O$103&gt;0)*('Original Data'!$R$4:$R$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$G$127</f>
         <v/>
       </c>
       <c r="H24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$R$4:$R$103&gt;0)*('Original Data'!$U$4:$U$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$H$127</f>
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$U$4:$U$103&gt;0)*('Original Data'!$X$4:$X$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$I$127</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$X$4:$X$103&gt;0)*('Original Data'!$AA$4:$AA$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$J$127</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$AA$4:$AA$103&gt;0)*('Original Data'!$AD$4:$AD$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$K$127</f>
         <v/>
       </c>
       <c r="L24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$AD$4:$AD$103&gt;0)*('Original Data'!$AG$4:$AG$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$L$127</f>
         <v/>
       </c>
       <c r="M24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$AG$4:$AG$103&gt;0)*('Original Data'!$AJ$4:$AJ$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$M$127</f>
         <v/>
       </c>
       <c r="N24" s="17">
-        <f>SUMPRODUCT(('Original Data'!$AJ$4:$AJ$103&gt;0)*('Original Data'!$AM$4:$AM$103&lt;=0)*1)</f>
+        <f>'Intermediate Calcs'!$N$127</f>
         <v/>
       </c>
     </row>
@@ -2401,55 +5942,55 @@
         </is>
       </c>
       <c r="B25" s="18">
-        <f>COUNTIF('Original Data'!$C$4:$C$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$B$128</f>
         <v/>
       </c>
       <c r="C25" s="18">
-        <f>COUNTIF('Original Data'!$F$4:$F$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$C$128</f>
         <v/>
       </c>
       <c r="D25" s="18">
-        <f>COUNTIF('Original Data'!$I$4:$I$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$D$128</f>
         <v/>
       </c>
       <c r="E25" s="18">
-        <f>COUNTIF('Original Data'!$L$4:$L$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$E$128</f>
         <v/>
       </c>
       <c r="F25" s="18">
-        <f>COUNTIF('Original Data'!$O$4:$O$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$F$128</f>
         <v/>
       </c>
       <c r="G25" s="18">
-        <f>COUNTIF('Original Data'!$R$4:$R$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$G$128</f>
         <v/>
       </c>
       <c r="H25" s="18">
-        <f>COUNTIF('Original Data'!$U$4:$U$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$H$128</f>
         <v/>
       </c>
       <c r="I25" s="18">
-        <f>COUNTIF('Original Data'!$X$4:$X$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$I$128</f>
         <v/>
       </c>
       <c r="J25" s="18">
-        <f>COUNTIF('Original Data'!$AA$4:$AA$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$J$128</f>
         <v/>
       </c>
       <c r="K25" s="18">
-        <f>COUNTIF('Original Data'!$AD$4:$AD$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$K$128</f>
         <v/>
       </c>
       <c r="L25" s="18">
-        <f>COUNTIF('Original Data'!$AG$4:$AG$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$L$128</f>
         <v/>
       </c>
       <c r="M25" s="18">
-        <f>COUNTIF('Original Data'!$AJ$4:$AJ$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$M$128</f>
         <v/>
       </c>
       <c r="N25" s="18">
-        <f>COUNTIF('Original Data'!$AM$4:$AM$103,"&gt;0")</f>
+        <f>'Intermediate Calcs'!$N$128</f>
         <v/>
       </c>
     </row>
@@ -3050,13 +6591,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN110"/>
+  <dimension ref="A1:AM110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -3067,115 +6608,115 @@
           <t>Customers</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="21" t="n">
         <v>44926</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="21" t="n">
         <v>44957</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E3" s="21" t="n">
         <v>44985</v>
       </c>
-      <c r="F3" s="20" t="n">
+      <c r="F3" s="21" t="n">
         <v>45016</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="G3" s="21" t="n">
         <v>45046</v>
       </c>
-      <c r="H3" s="20" t="n">
+      <c r="H3" s="21" t="n">
         <v>45077</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I3" s="21" t="n">
         <v>45107</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J3" s="21" t="n">
         <v>45138</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K3" s="21" t="n">
         <v>45169</v>
       </c>
-      <c r="L3" s="20" t="n">
+      <c r="L3" s="21" t="n">
         <v>45199</v>
       </c>
-      <c r="M3" s="20" t="n">
+      <c r="M3" s="21" t="n">
         <v>45230</v>
       </c>
-      <c r="N3" s="20" t="n">
+      <c r="N3" s="21" t="n">
         <v>45260</v>
       </c>
-      <c r="O3" s="20" t="n">
+      <c r="O3" s="21" t="n">
         <v>45291</v>
       </c>
-      <c r="P3" s="20" t="n">
+      <c r="P3" s="21" t="n">
         <v>45322</v>
       </c>
-      <c r="Q3" s="20" t="n">
+      <c r="Q3" s="21" t="n">
         <v>45351</v>
       </c>
-      <c r="R3" s="20" t="n">
+      <c r="R3" s="21" t="n">
         <v>45382</v>
       </c>
-      <c r="S3" s="20" t="n">
+      <c r="S3" s="21" t="n">
         <v>45412</v>
       </c>
-      <c r="T3" s="20" t="n">
+      <c r="T3" s="21" t="n">
         <v>45443</v>
       </c>
-      <c r="U3" s="20" t="n">
+      <c r="U3" s="21" t="n">
         <v>45473</v>
       </c>
-      <c r="V3" s="20" t="n">
+      <c r="V3" s="21" t="n">
         <v>45504</v>
       </c>
-      <c r="W3" s="20" t="n">
+      <c r="W3" s="21" t="n">
         <v>45535</v>
       </c>
-      <c r="X3" s="20" t="n">
+      <c r="X3" s="21" t="n">
         <v>45565</v>
       </c>
-      <c r="Y3" s="20" t="n">
+      <c r="Y3" s="21" t="n">
         <v>45596</v>
       </c>
-      <c r="Z3" s="20" t="n">
+      <c r="Z3" s="21" t="n">
         <v>45626</v>
       </c>
-      <c r="AA3" s="20" t="n">
+      <c r="AA3" s="21" t="n">
         <v>45657</v>
       </c>
-      <c r="AB3" s="20" t="n">
+      <c r="AB3" s="21" t="n">
         <v>45688</v>
       </c>
-      <c r="AC3" s="20" t="n">
+      <c r="AC3" s="21" t="n">
         <v>45716</v>
       </c>
-      <c r="AD3" s="20" t="n">
+      <c r="AD3" s="21" t="n">
         <v>45747</v>
       </c>
-      <c r="AE3" s="20" t="n">
+      <c r="AE3" s="21" t="n">
         <v>45777</v>
       </c>
-      <c r="AF3" s="20" t="n">
+      <c r="AF3" s="21" t="n">
         <v>45808</v>
       </c>
-      <c r="AG3" s="20" t="n">
+      <c r="AG3" s="21" t="n">
         <v>45838</v>
       </c>
-      <c r="AH3" s="20" t="n">
+      <c r="AH3" s="21" t="n">
         <v>45869</v>
       </c>
-      <c r="AI3" s="20" t="n">
+      <c r="AI3" s="21" t="n">
         <v>45900</v>
       </c>
-      <c r="AJ3" s="20" t="n">
+      <c r="AJ3" s="21" t="n">
         <v>45930</v>
       </c>
-      <c r="AK3" s="20" t="n">
+      <c r="AK3" s="21" t="n">
         <v>45961</v>
       </c>
-      <c r="AL3" s="20" t="n">
+      <c r="AL3" s="21" t="n">
         <v>45991</v>
       </c>
-      <c r="AM3" s="20" t="n">
+      <c r="AM3" s="21" t="n">
         <v>46022</v>
       </c>
     </row>
@@ -3294,10 +6835,6 @@
       <c r="AM4" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN4">
-        <f>IF($AM4*12&gt;10,RANK($AM4,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM4,$AM4)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -3414,10 +6951,6 @@
       <c r="AM5" t="n">
         <v>399</v>
       </c>
-      <c r="AN5">
-        <f>IF($AM5*12&gt;10,RANK($AM5,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM5,$AM5)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -3534,10 +7067,6 @@
       <c r="AM6" t="n">
         <v>306.46</v>
       </c>
-      <c r="AN6">
-        <f>IF($AM6*12&gt;10,RANK($AM6,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM6,$AM6)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -3654,10 +7183,6 @@
       <c r="AM7" t="n">
         <v>289</v>
       </c>
-      <c r="AN7">
-        <f>IF($AM7*12&gt;10,RANK($AM7,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM7,$AM7)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -3774,10 +7299,6 @@
       <c r="AM8" t="n">
         <v>225.75</v>
       </c>
-      <c r="AN8">
-        <f>IF($AM8*12&gt;10,RANK($AM8,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM8,$AM8)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -3894,10 +7415,6 @@
       <c r="AM9" t="n">
         <v>288.77</v>
       </c>
-      <c r="AN9">
-        <f>IF($AM9*12&gt;10,RANK($AM9,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM9,$AM9)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -4014,10 +7531,6 @@
       <c r="AM10" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN10">
-        <f>IF($AM10*12&gt;10,RANK($AM10,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM10,$AM10)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="B11" t="n">
@@ -4134,10 +7647,6 @@
       <c r="AM11" t="n">
         <v>0</v>
       </c>
-      <c r="AN11">
-        <f>IF($AM11*12&gt;10,RANK($AM11,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM11,$AM11)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -4254,10 +7763,6 @@
       <c r="AM12" t="n">
         <v>237.02</v>
       </c>
-      <c r="AN12">
-        <f>IF($AM12*12&gt;10,RANK($AM12,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM12,$AM12)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -4374,10 +7879,6 @@
       <c r="AM13" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN13">
-        <f>IF($AM13*12&gt;10,RANK($AM13,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM13,$AM13)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -4494,10 +7995,6 @@
       <c r="AM14" t="n">
         <v>179</v>
       </c>
-      <c r="AN14">
-        <f>IF($AM14*12&gt;10,RANK($AM14,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM14,$AM14)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -4614,10 +8111,6 @@
       <c r="AM15" t="n">
         <v>294</v>
       </c>
-      <c r="AN15">
-        <f>IF($AM15*12&gt;10,RANK($AM15,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM15,$AM15)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -4734,10 +8227,6 @@
       <c r="AM16" t="n">
         <v>381.92</v>
       </c>
-      <c r="AN16">
-        <f>IF($AM16*12&gt;10,RANK($AM16,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM16,$AM16)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
@@ -4854,10 +8343,6 @@
       <c r="AM17" t="n">
         <v>288.77</v>
       </c>
-      <c r="AN17">
-        <f>IF($AM17*12&gt;10,RANK($AM17,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM17,$AM17)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
@@ -4974,10 +8459,6 @@
       <c r="AM18" t="n">
         <v>179</v>
       </c>
-      <c r="AN18">
-        <f>IF($AM18*12&gt;10,RANK($AM18,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM18,$AM18)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
@@ -5094,10 +8575,6 @@
       <c r="AM19" t="n">
         <v>0</v>
       </c>
-      <c r="AN19">
-        <f>IF($AM19*12&gt;10,RANK($AM19,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM19,$AM19)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -5214,10 +8691,6 @@
       <c r="AM20" t="n">
         <v>288.77</v>
       </c>
-      <c r="AN20">
-        <f>IF($AM20*12&gt;10,RANK($AM20,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM20,$AM20)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
@@ -5334,10 +8807,6 @@
       <c r="AM21" t="n">
         <v>254.25</v>
       </c>
-      <c r="AN21">
-        <f>IF($AM21*12&gt;10,RANK($AM21,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM21,$AM21)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
@@ -5454,10 +8923,6 @@
       <c r="AM22" t="n">
         <v>116</v>
       </c>
-      <c r="AN22">
-        <f>IF($AM22*12&gt;10,RANK($AM22,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM22,$AM22)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="B23" t="n">
@@ -5574,10 +9039,6 @@
       <c r="AM23" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN23">
-        <f>IF($AM23*12&gt;10,RANK($AM23,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM23,$AM23)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
@@ -5694,10 +9155,6 @@
       <c r="AM24" t="n">
         <v>288.77</v>
       </c>
-      <c r="AN24">
-        <f>IF($AM24*12&gt;10,RANK($AM24,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM24,$AM24)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
@@ -5814,10 +9271,6 @@
       <c r="AM25" t="n">
         <v>309.47</v>
       </c>
-      <c r="AN25">
-        <f>IF($AM25*12&gt;10,RANK($AM25,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM25,$AM25)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
@@ -5934,10 +9387,6 @@
       <c r="AM26" t="n">
         <v>297.15</v>
       </c>
-      <c r="AN26">
-        <f>IF($AM26*12&gt;10,RANK($AM26,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM26,$AM26)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
@@ -6054,10 +9503,6 @@
       <c r="AM27" t="n">
         <v>352.44</v>
       </c>
-      <c r="AN27">
-        <f>IF($AM27*12&gt;10,RANK($AM27,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM27,$AM27)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
@@ -6174,10 +9619,6 @@
       <c r="AM28" t="n">
         <v>181.62</v>
       </c>
-      <c r="AN28">
-        <f>IF($AM28*12&gt;10,RANK($AM28,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM28,$AM28)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -6294,10 +9735,6 @@
       <c r="AM29" t="n">
         <v>191.75</v>
       </c>
-      <c r="AN29">
-        <f>IF($AM29*12&gt;10,RANK($AM29,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM29,$AM29)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -6414,10 +9851,6 @@
       <c r="AM30" t="n">
         <v>254.25</v>
       </c>
-      <c r="AN30">
-        <f>IF($AM30*12&gt;10,RANK($AM30,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM30,$AM30)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -6534,10 +9967,6 @@
       <c r="AM31" t="n">
         <v>0</v>
       </c>
-      <c r="AN31">
-        <f>IF($AM31*12&gt;10,RANK($AM31,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM31,$AM31)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -6654,10 +10083,6 @@
       <c r="AM32" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="AN32">
-        <f>IF($AM32*12&gt;10,RANK($AM32,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM32,$AM32)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -6774,10 +10199,6 @@
       <c r="AM33" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="AN33">
-        <f>IF($AM33*12&gt;10,RANK($AM33,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM33,$AM33)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -6894,10 +10315,6 @@
       <c r="AM34" t="n">
         <v>361.79</v>
       </c>
-      <c r="AN34">
-        <f>IF($AM34*12&gt;10,RANK($AM34,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM34,$AM34)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -7014,10 +10431,6 @@
       <c r="AM35" t="n">
         <v>307.04</v>
       </c>
-      <c r="AN35">
-        <f>IF($AM35*12&gt;10,RANK($AM35,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM35,$AM35)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -7134,10 +10547,6 @@
       <c r="AM36" t="n">
         <v>0</v>
       </c>
-      <c r="AN36">
-        <f>IF($AM36*12&gt;10,RANK($AM36,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM36,$AM36)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
@@ -7254,10 +10663,6 @@
       <c r="AM37" t="n">
         <v>247.37</v>
       </c>
-      <c r="AN37">
-        <f>IF($AM37*12&gt;10,RANK($AM37,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM37,$AM37)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
@@ -7374,10 +10779,6 @@
       <c r="AM38" t="n">
         <v>287.1</v>
       </c>
-      <c r="AN38">
-        <f>IF($AM38*12&gt;10,RANK($AM38,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM38,$AM38)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
@@ -7494,10 +10895,6 @@
       <c r="AM39" t="n">
         <v>0</v>
       </c>
-      <c r="AN39">
-        <f>IF($AM39*12&gt;10,RANK($AM39,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM39,$AM39)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
@@ -7614,10 +11011,6 @@
       <c r="AM40" t="n">
         <v>106.25</v>
       </c>
-      <c r="AN40">
-        <f>IF($AM40*12&gt;10,RANK($AM40,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM40,$AM40)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
@@ -7734,10 +11127,6 @@
       <c r="AM41" t="n">
         <v>226.67</v>
       </c>
-      <c r="AN41">
-        <f>IF($AM41*12&gt;10,RANK($AM41,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM41,$AM41)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
@@ -7854,10 +11243,6 @@
       <c r="AM42" t="n">
         <v>306.46</v>
       </c>
-      <c r="AN42">
-        <f>IF($AM42*12&gt;10,RANK($AM42,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM42,$AM42)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
@@ -7974,10 +11359,6 @@
       <c r="AM43" t="n">
         <v>247.37</v>
       </c>
-      <c r="AN43">
-        <f>IF($AM43*12&gt;10,RANK($AM43,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM43,$AM43)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
@@ -8094,10 +11475,6 @@
       <c r="AM44" t="n">
         <v>237.02</v>
       </c>
-      <c r="AN44">
-        <f>IF($AM44*12&gt;10,RANK($AM44,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM44,$AM44)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
@@ -8214,10 +11591,6 @@
       <c r="AM45" t="n">
         <v>69</v>
       </c>
-      <c r="AN45">
-        <f>IF($AM45*12&gt;10,RANK($AM45,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM45,$AM45)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
@@ -8334,10 +11707,6 @@
       <c r="AM46" t="n">
         <v>69</v>
       </c>
-      <c r="AN46">
-        <f>IF($AM46*12&gt;10,RANK($AM46,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM46,$AM46)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
@@ -8454,10 +11823,6 @@
       <c r="AM47" t="n">
         <v>69</v>
       </c>
-      <c r="AN47">
-        <f>IF($AM47*12&gt;10,RANK($AM47,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM47,$AM47)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
@@ -8574,10 +11939,6 @@
       <c r="AM48" t="n">
         <v>344.09</v>
       </c>
-      <c r="AN48">
-        <f>IF($AM48*12&gt;10,RANK($AM48,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM48,$AM48)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
@@ -8694,10 +12055,6 @@
       <c r="AM49" t="n">
         <v>226.67</v>
       </c>
-      <c r="AN49">
-        <f>IF($AM49*12&gt;10,RANK($AM49,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM49,$AM49)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
@@ -8814,10 +12171,6 @@
       <c r="AM50" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN50">
-        <f>IF($AM50*12&gt;10,RANK($AM50,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM50,$AM50)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="51">
       <c r="B51" t="n">
@@ -8934,10 +12287,6 @@
       <c r="AM51" t="n">
         <v>299.12</v>
       </c>
-      <c r="AN51">
-        <f>IF($AM51*12&gt;10,RANK($AM51,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM51,$AM51)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
@@ -9054,10 +12403,6 @@
       <c r="AM52" t="n">
         <v>294</v>
       </c>
-      <c r="AN52">
-        <f>IF($AM52*12&gt;10,RANK($AM52,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM52,$AM52)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
@@ -9174,10 +12519,6 @@
       <c r="AM53" t="n">
         <v>279.16</v>
       </c>
-      <c r="AN53">
-        <f>IF($AM53*12&gt;10,RANK($AM53,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM53,$AM53)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="54">
       <c r="B54" t="n">
@@ -9294,10 +12635,6 @@
       <c r="AM54" t="n">
         <v>361.22</v>
       </c>
-      <c r="AN54">
-        <f>IF($AM54*12&gt;10,RANK($AM54,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM54,$AM54)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="55">
       <c r="B55" t="n">
@@ -9414,10 +12751,6 @@
       <c r="AM55" t="n">
         <v>299.12</v>
       </c>
-      <c r="AN55">
-        <f>IF($AM55*12&gt;10,RANK($AM55,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM55,$AM55)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
@@ -9534,10 +12867,6 @@
       <c r="AM56" t="n">
         <v>381.22</v>
       </c>
-      <c r="AN56">
-        <f>IF($AM56*12&gt;10,RANK($AM56,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM56,$AM56)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="57">
       <c r="B57" t="n">
@@ -9654,10 +12983,6 @@
       <c r="AM57" t="n">
         <v>179</v>
       </c>
-      <c r="AN57">
-        <f>IF($AM57*12&gt;10,RANK($AM57,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM57,$AM57)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
@@ -9774,10 +13099,6 @@
       <c r="AM58" t="n">
         <v>99</v>
       </c>
-      <c r="AN58">
-        <f>IF($AM58*12&gt;10,RANK($AM58,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM58,$AM58)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
@@ -9894,10 +13215,6 @@
       <c r="AM59" t="n">
         <v>278.5</v>
       </c>
-      <c r="AN59">
-        <f>IF($AM59*12&gt;10,RANK($AM59,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM59,$AM59)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
@@ -10014,10 +13331,6 @@
       <c r="AM60" t="n">
         <v>0</v>
       </c>
-      <c r="AN60">
-        <f>IF($AM60*12&gt;10,RANK($AM60,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM60,$AM60)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
@@ -10134,10 +13447,6 @@
       <c r="AM61" t="n">
         <v>109</v>
       </c>
-      <c r="AN61">
-        <f>IF($AM61*12&gt;10,RANK($AM61,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM61,$AM61)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
@@ -10254,10 +13563,6 @@
       <c r="AM62" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN62">
-        <f>IF($AM62*12&gt;10,RANK($AM62,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM62,$AM62)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
@@ -10374,10 +13679,6 @@
       <c r="AM63" t="n">
         <v>199</v>
       </c>
-      <c r="AN63">
-        <f>IF($AM63*12&gt;10,RANK($AM63,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM63,$AM63)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
@@ -10494,10 +13795,6 @@
       <c r="AM64" t="n">
         <v>399.88</v>
       </c>
-      <c r="AN64">
-        <f>IF($AM64*12&gt;10,RANK($AM64,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM64,$AM64)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
@@ -10614,10 +13911,6 @@
       <c r="AM65" t="n">
         <v>361.22</v>
       </c>
-      <c r="AN65">
-        <f>IF($AM65*12&gt;10,RANK($AM65,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM65,$AM65)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
@@ -10734,10 +14027,6 @@
       <c r="AM66" t="n">
         <v>309.47</v>
       </c>
-      <c r="AN66">
-        <f>IF($AM66*12&gt;10,RANK($AM66,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM66,$AM66)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
@@ -10854,10 +14143,6 @@
       <c r="AM67" t="n">
         <v>309.47</v>
       </c>
-      <c r="AN67">
-        <f>IF($AM67*12&gt;10,RANK($AM67,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM67,$AM67)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
@@ -10974,10 +14259,6 @@
       <c r="AM68" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN68">
-        <f>IF($AM68*12&gt;10,RANK($AM68,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM68,$AM68)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
@@ -11094,10 +14375,6 @@
       <c r="AM69" t="n">
         <v>0</v>
       </c>
-      <c r="AN69">
-        <f>IF($AM69*12&gt;10,RANK($AM69,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM69,$AM69)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
@@ -11214,10 +14491,6 @@
       <c r="AM70" t="n">
         <v>257.72</v>
       </c>
-      <c r="AN70">
-        <f>IF($AM70*12&gt;10,RANK($AM70,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM70,$AM70)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
@@ -11334,10 +14607,6 @@
       <c r="AM71" t="n">
         <v>361.22</v>
       </c>
-      <c r="AN71">
-        <f>IF($AM71*12&gt;10,RANK($AM71,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM71,$AM71)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
@@ -11454,10 +14723,6 @@
       <c r="AM72" t="n">
         <v>0</v>
       </c>
-      <c r="AN72">
-        <f>IF($AM72*12&gt;10,RANK($AM72,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM72,$AM72)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
@@ -11574,10 +14839,6 @@
       <c r="AM73" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN73">
-        <f>IF($AM73*12&gt;10,RANK($AM73,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM73,$AM73)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
@@ -11694,10 +14955,6 @@
       <c r="AM74" t="n">
         <v>0</v>
       </c>
-      <c r="AN74">
-        <f>IF($AM74*12&gt;10,RANK($AM74,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM74,$AM74)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
@@ -11814,10 +15071,6 @@
       <c r="AM75" t="n">
         <v>288.15</v>
       </c>
-      <c r="AN75">
-        <f>IF($AM75*12&gt;10,RANK($AM75,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM75,$AM75)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
@@ -11934,10 +15187,6 @@
       <c r="AM76" t="n">
         <v>343.16</v>
       </c>
-      <c r="AN76">
-        <f>IF($AM76*12&gt;10,RANK($AM76,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM76,$AM76)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
@@ -12054,10 +15303,6 @@
       <c r="AM77" t="n">
         <v>0</v>
       </c>
-      <c r="AN77">
-        <f>IF($AM77*12&gt;10,RANK($AM77,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM77,$AM77)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
@@ -12174,10 +15419,6 @@
       <c r="AM78" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN78">
-        <f>IF($AM78*12&gt;10,RANK($AM78,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM78,$AM78)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
@@ -12294,10 +15535,6 @@
       <c r="AM79" t="n">
         <v>349.28</v>
       </c>
-      <c r="AN79">
-        <f>IF($AM79*12&gt;10,RANK($AM79,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM79,$AM79)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
@@ -12414,10 +15651,6 @@
       <c r="AM80" t="n">
         <v>288.15</v>
       </c>
-      <c r="AN80">
-        <f>IF($AM80*12&gt;10,RANK($AM80,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM80,$AM80)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
@@ -12534,10 +15767,6 @@
       <c r="AM81" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN81">
-        <f>IF($AM81*12&gt;10,RANK($AM81,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM81,$AM81)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
@@ -12654,10 +15883,6 @@
       <c r="AM82" t="n">
         <v>254.15</v>
       </c>
-      <c r="AN82">
-        <f>IF($AM82*12&gt;10,RANK($AM82,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM82,$AM82)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
@@ -12774,10 +15999,6 @@
       <c r="AM83" t="n">
         <v>191.75</v>
       </c>
-      <c r="AN83">
-        <f>IF($AM83*12&gt;10,RANK($AM83,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM83,$AM83)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
@@ -12894,10 +16115,6 @@
       <c r="AM84" t="n">
         <v>154.22</v>
       </c>
-      <c r="AN84">
-        <f>IF($AM84*12&gt;10,RANK($AM84,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM84,$AM84)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
@@ -13014,10 +16231,6 @@
       <c r="AM85" t="n">
         <v>288.77</v>
       </c>
-      <c r="AN85">
-        <f>IF($AM85*12&gt;10,RANK($AM85,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM85,$AM85)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
@@ -13134,10 +16347,6 @@
       <c r="AM86" t="n">
         <v>119</v>
       </c>
-      <c r="AN86">
-        <f>IF($AM86*12&gt;10,RANK($AM86,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM86,$AM86)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
@@ -13254,10 +16463,6 @@
       <c r="AM87" t="n">
         <v>109</v>
       </c>
-      <c r="AN87">
-        <f>IF($AM87*12&gt;10,RANK($AM87,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM87,$AM87)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="88">
       <c r="B88" t="n">
@@ -13374,10 +16579,6 @@
       <c r="AM88" t="n">
         <v>309.47</v>
       </c>
-      <c r="AN88">
-        <f>IF($AM88*12&gt;10,RANK($AM88,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM88,$AM88)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="89">
       <c r="B89" t="n">
@@ -13494,10 +16695,6 @@
       <c r="AM89" t="n">
         <v>100</v>
       </c>
-      <c r="AN89">
-        <f>IF($AM89*12&gt;10,RANK($AM89,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM89,$AM89)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="90">
       <c r="B90" t="n">
@@ -13614,10 +16811,6 @@
       <c r="AM90" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN90">
-        <f>IF($AM90*12&gt;10,RANK($AM90,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM90,$AM90)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="91">
       <c r="B91" t="n">
@@ -13734,10 +16927,6 @@
       <c r="AM91" t="n">
         <v>0</v>
       </c>
-      <c r="AN91">
-        <f>IF($AM91*12&gt;10,RANK($AM91,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM91,$AM91)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="92">
       <c r="B92" t="n">
@@ -13854,10 +17043,6 @@
       <c r="AM92" t="n">
         <v>0</v>
       </c>
-      <c r="AN92">
-        <f>IF($AM92*12&gt;10,RANK($AM92,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM92,$AM92)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="93">
       <c r="B93" t="n">
@@ -13974,10 +17159,6 @@
       <c r="AM93" t="n">
         <v>191.75</v>
       </c>
-      <c r="AN93">
-        <f>IF($AM93*12&gt;10,RANK($AM93,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM93,$AM93)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="94">
       <c r="B94" t="n">
@@ -14094,10 +17275,6 @@
       <c r="AM94" t="n">
         <v>361.22</v>
       </c>
-      <c r="AN94">
-        <f>IF($AM94*12&gt;10,RANK($AM94,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM94,$AM94)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="95">
       <c r="B95" t="n">
@@ -14214,10 +17391,6 @@
       <c r="AM95" t="n">
         <v>170.05</v>
       </c>
-      <c r="AN95">
-        <f>IF($AM95*12&gt;10,RANK($AM95,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM95,$AM95)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="96">
       <c r="B96" t="n">
@@ -14334,10 +17507,6 @@
       <c r="AM96" t="n">
         <v>185.27</v>
       </c>
-      <c r="AN96">
-        <f>IF($AM96*12&gt;10,RANK($AM96,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM96,$AM96)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="97">
       <c r="B97" t="n">
@@ -14454,10 +17623,6 @@
       <c r="AM97" t="n">
         <v>373.86</v>
       </c>
-      <c r="AN97">
-        <f>IF($AM97*12&gt;10,RANK($AM97,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM97,$AM97)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="98">
       <c r="B98" t="n">
@@ -14574,10 +17739,6 @@
       <c r="AM98" t="n">
         <v>129</v>
       </c>
-      <c r="AN98">
-        <f>IF($AM98*12&gt;10,RANK($AM98,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM98,$AM98)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="99">
       <c r="B99" t="n">
@@ -14694,10 +17855,6 @@
       <c r="AM99" t="n">
         <v>294</v>
       </c>
-      <c r="AN99">
-        <f>IF($AM99*12&gt;10,RANK($AM99,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM99,$AM99)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="100">
       <c r="B100" t="n">
@@ -14814,10 +17971,6 @@
       <c r="AM100" t="n">
         <v>0</v>
       </c>
-      <c r="AN100">
-        <f>IF($AM100*12&gt;10,RANK($AM100,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM100,$AM100)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="101">
       <c r="B101" t="n">
@@ -14934,10 +18087,6 @@
       <c r="AM101" t="n">
         <v>0</v>
       </c>
-      <c r="AN101">
-        <f>IF($AM101*12&gt;10,RANK($AM101,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM101,$AM101)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="102">
       <c r="B102" t="n">
@@ -15054,10 +18203,6 @@
       <c r="AM102" t="n">
         <v>201.94</v>
       </c>
-      <c r="AN102">
-        <f>IF($AM102*12&gt;10,RANK($AM102,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM102,$AM102)-1,"N/A")</f>
-        <v/>
-      </c>
     </row>
     <row r="103">
       <c r="B103" t="n">
@@ -15173,10 +18318,6 @@
       </c>
       <c r="AM103" t="n">
         <v>0</v>
-      </c>
-      <c r="AN103">
-        <f>IF($AM103*12&gt;10,RANK($AM103,$AM$4:$AM$103,0)+COUNTIF($AM$4:$AM103,$AM103)-1,"N/A")</f>
-        <v/>
       </c>
     </row>
     <row r="104"/>
@@ -15191,7 +18332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15245,7 +18386,7 @@
       <c r="R1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>($ Actuals)</t>
         </is>
@@ -15365,34 +18506,34 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A4,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A4,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A4,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A4,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A4,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A4,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A4,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A4,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A4,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A4,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="23">
         <f>IF(C4=0,0,(F4/C4)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="23">
         <f>IF(F17=0,0,F4/F17)</f>
         <v/>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="23">
         <f>SUM(H$4:H4)</f>
         <v/>
       </c>
@@ -15408,27 +18549,27 @@
         <f>F4-E4</f>
         <v/>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="23">
         <f>IF(L17=0,0,L4/L17)</f>
         <v/>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="24">
         <f>IF(C4=0,0,F4/C4)</f>
         <v/>
       </c>
-      <c r="O4" s="22">
+      <c r="O4" s="23">
         <f>IF(C4=0,0,D4/C4-1)</f>
         <v/>
       </c>
-      <c r="P4" s="22">
+      <c r="P4" s="23">
         <f>IF(D4=0,0,E4/D4-1)</f>
         <v/>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4" s="23">
         <f>IF(E4=0,0,F4/E4-1)</f>
         <v/>
       </c>
-      <c r="R4" s="24" t="inlineStr">
+      <c r="R4" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15439,34 +18580,34 @@
         <v>2</v>
       </c>
       <c r="B5" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A5,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A5,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A5,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A5,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A5,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A5,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A5,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A5,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A5,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A5,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
         <f>IF(C5=0,0,(F5/C5)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="23">
         <f>IF(F17=0,0,F5/F17)</f>
         <v/>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="23">
         <f>SUM(H$4:H5)</f>
         <v/>
       </c>
@@ -15482,27 +18623,27 @@
         <f>F5-E5</f>
         <v/>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="23">
         <f>IF(L17=0,0,L5/L17)</f>
         <v/>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="24">
         <f>IF(C5=0,0,F5/C5)</f>
         <v/>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="23">
         <f>IF(C5=0,0,D5/C5-1)</f>
         <v/>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="23">
         <f>IF(D5=0,0,E5/D5-1)</f>
         <v/>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="23">
         <f>IF(E5=0,0,F5/E5-1)</f>
         <v/>
       </c>
-      <c r="R5" s="24" t="inlineStr">
+      <c r="R5" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15513,34 +18654,34 @@
         <v>3</v>
       </c>
       <c r="B6" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A6,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A6,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A6,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A6,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A6,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A6,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A6,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A6,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A6,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A6,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
         <f>IF(C6=0,0,(F6/C6)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="23">
         <f>IF(F17=0,0,F6/F17)</f>
         <v/>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="23">
         <f>SUM(H$4:H6)</f>
         <v/>
       </c>
@@ -15556,27 +18697,27 @@
         <f>F6-E6</f>
         <v/>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="23">
         <f>IF(L17=0,0,L6/L17)</f>
         <v/>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="24">
         <f>IF(C6=0,0,F6/C6)</f>
         <v/>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="23">
         <f>IF(C6=0,0,D6/C6-1)</f>
         <v/>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="23">
         <f>IF(D6=0,0,E6/D6-1)</f>
         <v/>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="23">
         <f>IF(E6=0,0,F6/E6-1)</f>
         <v/>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="R6" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15587,34 +18728,34 @@
         <v>4</v>
       </c>
       <c r="B7" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A7,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A7,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A7,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A7,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A7,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A7,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A7,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A7,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A7,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A7,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="23">
         <f>IF(C7=0,0,(F7/C7)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <f>IF(F17=0,0,F7/F17)</f>
         <v/>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="23">
         <f>SUM(H$4:H7)</f>
         <v/>
       </c>
@@ -15630,27 +18771,27 @@
         <f>F7-E7</f>
         <v/>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="23">
         <f>IF(L17=0,0,L7/L17)</f>
         <v/>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="24">
         <f>IF(C7=0,0,F7/C7)</f>
         <v/>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="23">
         <f>IF(C7=0,0,D7/C7-1)</f>
         <v/>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="23">
         <f>IF(D7=0,0,E7/D7-1)</f>
         <v/>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7" s="23">
         <f>IF(E7=0,0,F7/E7-1)</f>
         <v/>
       </c>
-      <c r="R7" s="24" t="inlineStr">
+      <c r="R7" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15661,34 +18802,34 @@
         <v>5</v>
       </c>
       <c r="B8" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A8,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A8,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A8,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A8,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A8,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A8,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A8,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A8,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A8,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A8,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="23">
         <f>IF(C8=0,0,(F8/C8)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="23">
         <f>IF(F17=0,0,F8/F17)</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="23">
         <f>SUM(H$4:H8)</f>
         <v/>
       </c>
@@ -15704,27 +18845,27 @@
         <f>F8-E8</f>
         <v/>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="23">
         <f>IF(L17=0,0,L8/L17)</f>
         <v/>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="24">
         <f>IF(C8=0,0,F8/C8)</f>
         <v/>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="23">
         <f>IF(C8=0,0,D8/C8-1)</f>
         <v/>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="23">
         <f>IF(D8=0,0,E8/D8-1)</f>
         <v/>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="23">
         <f>IF(E8=0,0,F8/E8-1)</f>
         <v/>
       </c>
-      <c r="R8" s="24" t="inlineStr">
+      <c r="R8" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15735,34 +18876,34 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A9,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A9,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A9,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A9,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A9,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A9,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A9,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A9,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A9,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A9,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="23">
         <f>IF(C9=0,0,(F9/C9)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="23">
         <f>IF(F17=0,0,F9/F17)</f>
         <v/>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="23">
         <f>SUM(H$4:H9)</f>
         <v/>
       </c>
@@ -15778,27 +18919,27 @@
         <f>F9-E9</f>
         <v/>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="23">
         <f>IF(L17=0,0,L9/L17)</f>
         <v/>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="24">
         <f>IF(C9=0,0,F9/C9)</f>
         <v/>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="23">
         <f>IF(C9=0,0,D9/C9-1)</f>
         <v/>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="23">
         <f>IF(D9=0,0,E9/D9-1)</f>
         <v/>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="23">
         <f>IF(E9=0,0,F9/E9-1)</f>
         <v/>
       </c>
-      <c r="R9" s="24" t="inlineStr">
+      <c r="R9" s="25" t="inlineStr">
         <is>
           <t>Mar-23</t>
         </is>
@@ -15809,34 +18950,34 @@
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A10,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A10,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A10,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A10,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A10,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A10,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A10,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A10,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A10,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A10,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="23">
         <f>IF(C10=0,0,(F10/C10)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="23">
         <f>IF(F17=0,0,F10/F17)</f>
         <v/>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="23">
         <f>SUM(H$4:H10)</f>
         <v/>
       </c>
@@ -15852,27 +18993,27 @@
         <f>F10-E10</f>
         <v/>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="23">
         <f>IF(L17=0,0,L10/L17)</f>
         <v/>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="24">
         <f>IF(C10=0,0,F10/C10)</f>
         <v/>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="23">
         <f>IF(C10=0,0,D10/C10-1)</f>
         <v/>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="23">
         <f>IF(D10=0,0,E10/D10-1)</f>
         <v/>
       </c>
-      <c r="Q10" s="22">
+      <c r="Q10" s="23">
         <f>IF(E10=0,0,F10/E10-1)</f>
         <v/>
       </c>
-      <c r="R10" s="24" t="inlineStr">
+      <c r="R10" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -15883,34 +19024,34 @@
         <v>8</v>
       </c>
       <c r="B11" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A11,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A11,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A11,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A11,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A11,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A11,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A11,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A11,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A11,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A11,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="23">
         <f>IF(C11=0,0,(F11/C11)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="23">
         <f>IF(F17=0,0,F11/F17)</f>
         <v/>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="23">
         <f>SUM(H$4:H11)</f>
         <v/>
       </c>
@@ -15926,27 +19067,27 @@
         <f>F11-E11</f>
         <v/>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="23">
         <f>IF(L17=0,0,L11/L17)</f>
         <v/>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="24">
         <f>IF(C11=0,0,F11/C11)</f>
         <v/>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="23">
         <f>IF(C11=0,0,D11/C11-1)</f>
         <v/>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="23">
         <f>IF(D11=0,0,E11/D11-1)</f>
         <v/>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11" s="23">
         <f>IF(E11=0,0,F11/E11-1)</f>
         <v/>
       </c>
-      <c r="R11" s="24" t="inlineStr">
+      <c r="R11" s="25" t="inlineStr">
         <is>
           <t>Jun-25</t>
         </is>
@@ -15957,34 +19098,34 @@
         <v>9</v>
       </c>
       <c r="B12" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A12,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A12,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A12,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A12,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A12,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A12,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A12,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A12,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A12,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A12,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
         <f>IF(C12=0,0,(F12/C12)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="23">
         <f>IF(F17=0,0,F12/F17)</f>
         <v/>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="23">
         <f>SUM(H$4:H12)</f>
         <v/>
       </c>
@@ -16000,27 +19141,27 @@
         <f>F12-E12</f>
         <v/>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="23">
         <f>IF(L17=0,0,L12/L17)</f>
         <v/>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="24">
         <f>IF(C12=0,0,F12/C12)</f>
         <v/>
       </c>
-      <c r="O12" s="22">
+      <c r="O12" s="23">
         <f>IF(C12=0,0,D12/C12-1)</f>
         <v/>
       </c>
-      <c r="P12" s="22">
+      <c r="P12" s="23">
         <f>IF(D12=0,0,E12/D12-1)</f>
         <v/>
       </c>
-      <c r="Q12" s="22">
+      <c r="Q12" s="23">
         <f>IF(E12=0,0,F12/E12-1)</f>
         <v/>
       </c>
-      <c r="R12" s="24" t="inlineStr">
+      <c r="R12" s="25" t="inlineStr">
         <is>
           <t>Jun-25</t>
         </is>
@@ -16031,34 +19172,34 @@
         <v>10</v>
       </c>
       <c r="B13" s="4">
-        <f>IFERROR(INDEX('Original Data'!$B$4:$B$103,MATCH($A13,'Original Data'!$AN$4:$AN$103,0),1),"")</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$A$3:$A$102,MATCH($A13,'Intermediate Calcs'!$F$3:$F$102,0),1),"")</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX('Original Data'!$C$4:$C$103,MATCH($A13,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$B$3:$B$102,MATCH($A13,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IFERROR(INDEX('Original Data'!$O$4:$O$103,MATCH($A13,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$C$3:$C$102,MATCH($A13,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AA$4:$AA$103,MATCH($A13,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
+        <f>IFERROR(INDEX('Intermediate Calcs'!$D$3:$D$102,MATCH($A13,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
         <v/>
       </c>
       <c r="F13" s="6">
-        <f>IFERROR(INDEX('Original Data'!$AM$4:$AM$103,MATCH($A13,'Original Data'!$AN$4:$AN$103,0),1)*12,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="22">
+        <f>IFERROR(INDEX('Intermediate Calcs'!$E$3:$E$102,MATCH($A13,'Intermediate Calcs'!$F$3:$F$102,0),1),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="23">
         <f>IF(C13=0,0,(F13/C13)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="23">
         <f>IF(F17=0,0,F13/F17)</f>
         <v/>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="23">
         <f>SUM(H$4:H13)</f>
         <v/>
       </c>
@@ -16074,27 +19215,27 @@
         <f>F13-E13</f>
         <v/>
       </c>
-      <c r="M13" s="22">
+      <c r="M13" s="23">
         <f>IF(L17=0,0,L13/L17)</f>
         <v/>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="24">
         <f>IF(C13=0,0,F13/C13)</f>
         <v/>
       </c>
-      <c r="O13" s="22">
+      <c r="O13" s="23">
         <f>IF(C13=0,0,D13/C13-1)</f>
         <v/>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="23">
         <f>IF(D13=0,0,E13/D13-1)</f>
         <v/>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13" s="23">
         <f>IF(E13=0,0,F13/E13-1)</f>
         <v/>
       </c>
-      <c r="R13" s="24" t="inlineStr">
+      <c r="R13" s="25" t="inlineStr">
         <is>
           <t>Dec-22</t>
         </is>
@@ -16123,15 +19264,15 @@
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <f>IF(C14=0,0,(F14/C14)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <f>IF(F17=0,0,F14/F17)</f>
         <v/>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="26">
         <f>SUM(H4:H13)</f>
         <v/>
       </c>
@@ -16147,32 +19288,32 @@
         <f>SUM(L4:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="26">
         <f>IF(L17=0,0,L14/L17)</f>
         <v/>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="27">
         <f>IF(C14=0,0,F14/C14)</f>
         <v/>
       </c>
-      <c r="O14" s="25">
+      <c r="O14" s="26">
         <f>IF(C14=0,0,D14/C14-1)</f>
         <v/>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="26">
         <f>IF(D14=0,0,E14/D14-1)</f>
         <v/>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="26">
         <f>IF(E14=0,0,F14/E14-1)</f>
         <v/>
       </c>
-      <c r="R14" s="27" t="n"/>
+      <c r="R14" s="28" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4">
-        <f>"Other ("&amp;COUNTIFS('Original Data'!$AM$4:$AM$103,"&gt;"&amp;10/12)-10&amp;" Customers)"</f>
+        <f>"Other ("&amp;COUNTIFS('Intermediate Calcs'!$E$3:$E$102,"&gt;"&amp;10)-10&amp;" Customers)"</f>
         <v/>
       </c>
       <c r="C16" s="6">
@@ -16191,15 +19332,15 @@
         <f>F17-F14</f>
         <v/>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <f>IF(C16=0,0,(F16/C16)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <f>IF(F17=0,0,F16/F17)</f>
         <v/>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
+      <c r="I16" s="23" t="inlineStr"/>
       <c r="J16" s="6">
         <f>J17-J14</f>
         <v/>
@@ -16212,27 +19353,27 @@
         <f>L17-L14</f>
         <v/>
       </c>
-      <c r="M16" s="22">
+      <c r="M16" s="23">
         <f>IF(L17=0,0,L16/L17)</f>
         <v/>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="24">
         <f>IF(C16=0,0,F16/C16)</f>
         <v/>
       </c>
-      <c r="O16" s="22">
+      <c r="O16" s="23">
         <f>IF(C16=0,0,D16/C16-1)</f>
         <v/>
       </c>
-      <c r="P16" s="22">
+      <c r="P16" s="23">
         <f>IF(D16=0,0,E16/D16-1)</f>
         <v/>
       </c>
-      <c r="Q16" s="22">
+      <c r="Q16" s="23">
         <f>IF(E16=0,0,F16/E16-1)</f>
         <v/>
       </c>
-      <c r="R16" s="24" t="n"/>
+      <c r="R16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -16242,30 +19383,30 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>SUM('Original Data'!$C$4:$C$103)*12</f>
+        <f>SUM('Intermediate Calcs'!$B$3:$B$102)</f>
         <v/>
       </c>
       <c r="D17" s="8">
-        <f>SUM('Original Data'!$O$4:$O$103)*12</f>
+        <f>SUM('Intermediate Calcs'!$C$3:$C$102)</f>
         <v/>
       </c>
       <c r="E17" s="8">
-        <f>SUM('Original Data'!$AA$4:$AA$103)*12</f>
+        <f>SUM('Intermediate Calcs'!$D$3:$D$102)</f>
         <v/>
       </c>
       <c r="F17" s="8">
-        <f>SUM('Original Data'!$AM$4:$AM$103)*12</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
+        <f>SUM('Intermediate Calcs'!$E$3:$E$102)</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
         <f>IF(C17=0,0,(F17/C17)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <f>IF(F17=0,0,F17/F17)</f>
         <v/>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <f>IF(F17=0,0,F17/F17)</f>
         <v/>
       </c>
@@ -16281,27 +19422,27 @@
         <f>F17-E17</f>
         <v/>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="26">
         <f>IF(L17=0,0,L17/L17)</f>
         <v/>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="27">
         <f>IF(C17=0,0,F17/C17)</f>
         <v/>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="26">
         <f>IF(C17=0,0,D17/C17-1)</f>
         <v/>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="26">
         <f>IF(D17=0,0,E17/D17-1)</f>
         <v/>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="26">
         <f>IF(E17=0,0,F17/E17-1)</f>
         <v/>
       </c>
-      <c r="R17" s="27" t="n"/>
+      <c r="R17" s="28" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
@@ -16326,15 +19467,15 @@
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <f>IF(C19=0,0,(F19/C19)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="23">
         <f>IF(F17=0,0,F19/F17)</f>
         <v/>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="23">
         <f>SUM(H4:H8)</f>
         <v/>
       </c>
@@ -16350,27 +19491,27 @@
         <f>SUM(L4:L8)</f>
         <v/>
       </c>
-      <c r="M19" s="22">
+      <c r="M19" s="23">
         <f>IF(L17=0,0,L19/L17)</f>
         <v/>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="24">
         <f>IF(C19=0,0,F19/C19)</f>
         <v/>
       </c>
-      <c r="O19" s="22">
+      <c r="O19" s="23">
         <f>IF(C19=0,0,D19/C19-1)</f>
         <v/>
       </c>
-      <c r="P19" s="22">
+      <c r="P19" s="23">
         <f>IF(D19=0,0,E19/D19-1)</f>
         <v/>
       </c>
-      <c r="Q19" s="22">
+      <c r="Q19" s="23">
         <f>IF(E19=0,0,F19/E19-1)</f>
         <v/>
       </c>
-      <c r="R19" s="24" t="n"/>
+      <c r="R19" s="25" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
@@ -16395,15 +19536,15 @@
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <f>IF(C20=0,0,(F20/C20)^(1/3)-1)</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <f>IF(F17=0,0,F20/F17)</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="23">
         <f>SUM(H4:H13)</f>
         <v/>
       </c>
@@ -16419,27 +19560,27 @@
         <f>SUM(L4:L13)</f>
         <v/>
       </c>
-      <c r="M20" s="22">
+      <c r="M20" s="23">
         <f>IF(L17=0,0,L20/L17)</f>
         <v/>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="24">
         <f>IF(C20=0,0,F20/C20)</f>
         <v/>
       </c>
-      <c r="O20" s="22">
+      <c r="O20" s="23">
         <f>IF(C20=0,0,D20/C20-1)</f>
         <v/>
       </c>
-      <c r="P20" s="22">
+      <c r="P20" s="23">
         <f>IF(D20=0,0,E20/D20-1)</f>
         <v/>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20" s="23">
         <f>IF(E20=0,0,F20/E20-1)</f>
         <v/>
       </c>
-      <c r="R20" s="24" t="n"/>
+      <c r="R20" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
